--- a/research/traditional_assets/database/data/iceland/iceland_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_telecom_services.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07388429899187365</v>
+        <v>0.07377253039388991</v>
       </c>
       <c r="C2">
-        <v>367.4005223353898</v>
+        <v>365.1775252642004</v>
       </c>
       <c r="D2">
-        <v>358.8905223353898</v>
+        <v>360.3245252642004</v>
       </c>
       <c r="E2">
-        <v>-119.1</v>
+        <v>-115.443</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.657</v>
       </c>
       <c r="G2">
         <v>8.51</v>
@@ -1582,28 +1582,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1839471</v>
       </c>
       <c r="N2">
-        <v>50.22333333333333</v>
+        <v>50.03938623333333</v>
       </c>
       <c r="O2">
-        <v>10.04466666666667</v>
+        <v>10.00787724666667</v>
       </c>
       <c r="P2">
-        <v>40.17866666666666</v>
+        <v>40.03150898666667</v>
       </c>
       <c r="Q2">
-        <v>47.68866666666666</v>
+        <v>47.54150898666666</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07388429899187365</v>
+        <v>0.07411124282211103</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5370538146839923</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>273.0313950768092</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07377253039388991</v>
+        <v>0.07366076179590615</v>
       </c>
       <c r="C3">
-        <v>365.1775252642004</v>
+        <v>362.9660337288634</v>
       </c>
       <c r="D3">
-        <v>360.3245252642004</v>
+        <v>361.7700337288634</v>
       </c>
       <c r="E3">
-        <v>-115.443</v>
+        <v>-111.786</v>
       </c>
       <c r="F3">
-        <v>3.657</v>
+        <v>7.314</v>
       </c>
       <c r="G3">
         <v>8.51</v>
@@ -1664,28 +1664,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M3">
-        <v>0.1839471</v>
+        <v>0.3678942</v>
       </c>
       <c r="N3">
-        <v>50.03938623333333</v>
+        <v>49.85543913333333</v>
       </c>
       <c r="O3">
-        <v>10.00787724666667</v>
+        <v>9.971087826666666</v>
       </c>
       <c r="P3">
-        <v>40.03150898666667</v>
+        <v>39.88435130666666</v>
       </c>
       <c r="Q3">
-        <v>47.54150898666666</v>
+        <v>47.39435130666666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07411124282211103</v>
+        <v>0.07434281815908791</v>
       </c>
       <c r="T3">
-        <v>0.5370538146839923</v>
+        <v>0.5414467132540629</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>273.0313950768092</v>
+        <v>136.5156975384046</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07366076179590615</v>
+        <v>0.07354899319792242</v>
       </c>
       <c r="C4">
-        <v>362.9660337288634</v>
+        <v>360.7661867568669</v>
       </c>
       <c r="D4">
-        <v>361.7700337288634</v>
+        <v>363.227186756867</v>
       </c>
       <c r="E4">
-        <v>-111.786</v>
+        <v>-108.129</v>
       </c>
       <c r="F4">
-        <v>7.314</v>
+        <v>10.971</v>
       </c>
       <c r="G4">
         <v>8.51</v>
@@ -1746,28 +1746,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M4">
-        <v>0.3678942</v>
+        <v>0.5518413</v>
       </c>
       <c r="N4">
-        <v>49.85543913333333</v>
+        <v>49.67149203333333</v>
       </c>
       <c r="O4">
-        <v>9.971087826666666</v>
+        <v>9.934298406666667</v>
       </c>
       <c r="P4">
-        <v>39.88435130666666</v>
+        <v>39.73719362666667</v>
       </c>
       <c r="Q4">
-        <v>47.39435130666666</v>
+        <v>47.24719362666666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07434281815908791</v>
+        <v>0.07457916824528084</v>
       </c>
       <c r="T4">
-        <v>0.5414467132540629</v>
+        <v>0.5459301870523824</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>136.5156975384046</v>
+        <v>91.01046502560307</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07354899319792242</v>
+        <v>0.07343722459993868</v>
       </c>
       <c r="C5">
-        <v>360.7661867568669</v>
+        <v>358.5781256246824</v>
       </c>
       <c r="D5">
-        <v>363.227186756867</v>
+        <v>364.6961256246824</v>
       </c>
       <c r="E5">
-        <v>-108.129</v>
+        <v>-104.472</v>
       </c>
       <c r="F5">
-        <v>10.971</v>
+        <v>14.628</v>
       </c>
       <c r="G5">
         <v>8.51</v>
@@ -1828,28 +1828,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M5">
-        <v>0.5518413</v>
+        <v>0.7357884</v>
       </c>
       <c r="N5">
-        <v>49.67149203333333</v>
+        <v>49.48754493333333</v>
       </c>
       <c r="O5">
-        <v>9.934298406666667</v>
+        <v>9.897508986666667</v>
       </c>
       <c r="P5">
-        <v>39.73719362666667</v>
+        <v>39.59003594666667</v>
       </c>
       <c r="Q5">
-        <v>47.24719362666666</v>
+        <v>47.10003594666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07457916824528084</v>
+        <v>0.07482044229160278</v>
       </c>
       <c r="T5">
-        <v>0.5459301870523824</v>
+        <v>0.5505070665548337</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>91.01046502560307</v>
+        <v>68.2578487692023</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07343722459993868</v>
+        <v>0.07332545600195492</v>
       </c>
       <c r="C6">
-        <v>358.5781256246824</v>
+        <v>356.4019939034235</v>
       </c>
       <c r="D6">
-        <v>364.6961256246824</v>
+        <v>366.1769939034235</v>
       </c>
       <c r="E6">
-        <v>-104.472</v>
+        <v>-100.815</v>
       </c>
       <c r="F6">
-        <v>14.628</v>
+        <v>18.285</v>
       </c>
       <c r="G6">
         <v>8.51</v>
@@ -1910,28 +1910,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M6">
-        <v>0.7357884</v>
+        <v>0.9197354999999999</v>
       </c>
       <c r="N6">
-        <v>49.48754493333333</v>
+        <v>49.30359783333333</v>
       </c>
       <c r="O6">
-        <v>9.897508986666667</v>
+        <v>9.860719566666667</v>
       </c>
       <c r="P6">
-        <v>39.59003594666667</v>
+        <v>39.44287826666666</v>
       </c>
       <c r="Q6">
-        <v>47.10003594666667</v>
+        <v>46.95287826666666</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07482044229160278</v>
+        <v>0.0750667957915315</v>
       </c>
       <c r="T6">
-        <v>0.5505070665548337</v>
+        <v>0.5551803014152312</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>68.2578487692023</v>
+        <v>54.60627901536184</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07332545600195492</v>
+        <v>0.07321368740397118</v>
       </c>
       <c r="C7">
-        <v>356.4019939034235</v>
+        <v>354.2379375056242</v>
       </c>
       <c r="D7">
-        <v>366.1769939034235</v>
+        <v>367.6699375056242</v>
       </c>
       <c r="E7">
-        <v>-100.815</v>
+        <v>-97.15799999999999</v>
       </c>
       <c r="F7">
-        <v>18.285</v>
+        <v>21.942</v>
       </c>
       <c r="G7">
         <v>8.51</v>
@@ -1992,28 +1992,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M7">
-        <v>0.9197354999999999</v>
+        <v>1.1036826</v>
       </c>
       <c r="N7">
-        <v>49.30359783333333</v>
+        <v>49.11965073333333</v>
       </c>
       <c r="O7">
-        <v>9.860719566666667</v>
+        <v>9.823930146666667</v>
       </c>
       <c r="P7">
-        <v>39.44287826666666</v>
+        <v>39.29572058666666</v>
       </c>
       <c r="Q7">
-        <v>46.95287826666666</v>
+        <v>46.80572058666666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0750667957915315</v>
+        <v>0.07531839085528849</v>
       </c>
       <c r="T7">
-        <v>0.5551803014152312</v>
+        <v>0.5599529668045735</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.60627901536184</v>
+        <v>45.50523251280153</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07321368740397118</v>
+        <v>0.07310191880598743</v>
       </c>
       <c r="C8">
-        <v>354.2379375056242</v>
+        <v>352.0861047331658</v>
       </c>
       <c r="D8">
-        <v>367.6699375056242</v>
+        <v>369.1751047331658</v>
       </c>
       <c r="E8">
-        <v>-97.15799999999999</v>
+        <v>-93.501</v>
       </c>
       <c r="F8">
-        <v>21.942</v>
+        <v>25.599</v>
       </c>
       <c r="G8">
         <v>8.51</v>
@@ -2074,28 +2074,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M8">
-        <v>1.1036826</v>
+        <v>1.2876297</v>
       </c>
       <c r="N8">
-        <v>49.11965073333333</v>
+        <v>48.93570363333333</v>
       </c>
       <c r="O8">
-        <v>9.823930146666667</v>
+        <v>9.787140726666667</v>
       </c>
       <c r="P8">
-        <v>39.29572058666666</v>
+        <v>39.14856290666667</v>
       </c>
       <c r="Q8">
-        <v>46.80572058666666</v>
+        <v>46.65856290666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07531839085528849</v>
+        <v>0.07557539656557788</v>
       </c>
       <c r="T8">
-        <v>0.5599529668045735</v>
+        <v>0.5648282701592779</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.50523251280153</v>
+        <v>39.00448501097275</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07310191880598742</v>
+        <v>0.07299015020800369</v>
       </c>
       <c r="C9">
-        <v>352.0861047331659</v>
+        <v>349.9466463263851</v>
       </c>
       <c r="D9">
-        <v>369.1751047331659</v>
+        <v>370.6926463263852</v>
       </c>
       <c r="E9">
-        <v>-93.50099999999999</v>
+        <v>-89.84399999999999</v>
       </c>
       <c r="F9">
-        <v>25.599</v>
+        <v>29.256</v>
       </c>
       <c r="G9">
         <v>8.51</v>
@@ -2156,28 +2156,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M9">
-        <v>1.2876297</v>
+        <v>1.4715768</v>
       </c>
       <c r="N9">
-        <v>48.93570363333333</v>
+        <v>48.75175653333333</v>
       </c>
       <c r="O9">
-        <v>9.787140726666667</v>
+        <v>9.750351306666666</v>
       </c>
       <c r="P9">
-        <v>39.14856290666667</v>
+        <v>39.00140522666666</v>
       </c>
       <c r="Q9">
-        <v>46.65856290666667</v>
+        <v>46.51140522666666</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07557539656557788</v>
+        <v>0.07583798935652573</v>
       </c>
       <c r="T9">
-        <v>0.5648282701592779</v>
+        <v>0.5698095583695193</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.00448501097275</v>
+        <v>34.12892438460115</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07299015020800369</v>
+        <v>0.07287838161001993</v>
       </c>
       <c r="C10">
-        <v>349.9466463263851</v>
+        <v>347.8197155143995</v>
       </c>
       <c r="D10">
-        <v>370.6926463263852</v>
+        <v>372.2227155143996</v>
       </c>
       <c r="E10">
-        <v>-89.84399999999999</v>
+        <v>-86.187</v>
       </c>
       <c r="F10">
-        <v>29.256</v>
+        <v>32.913</v>
       </c>
       <c r="G10">
         <v>8.51</v>
@@ -2238,28 +2238,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M10">
-        <v>1.4715768</v>
+        <v>1.6555239</v>
       </c>
       <c r="N10">
-        <v>48.75175653333333</v>
+        <v>48.56780943333333</v>
       </c>
       <c r="O10">
-        <v>9.750351306666666</v>
+        <v>9.713561886666668</v>
       </c>
       <c r="P10">
-        <v>39.00140522666666</v>
+        <v>38.85424754666666</v>
       </c>
       <c r="Q10">
-        <v>46.51140522666666</v>
+        <v>46.36424754666666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07583798935652573</v>
+        <v>0.07610635341760431</v>
       </c>
       <c r="T10">
-        <v>0.5698095583695193</v>
+        <v>0.5749003254415243</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.12892438460115</v>
+        <v>30.33682167520103</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07287838161001993</v>
+        <v>0.07276661301203619</v>
       </c>
       <c r="C11">
-        <v>347.8197155143995</v>
+        <v>345.7054680666826</v>
       </c>
       <c r="D11">
-        <v>372.2227155143996</v>
+        <v>373.7654680666826</v>
       </c>
       <c r="E11">
-        <v>-86.187</v>
+        <v>-82.53</v>
       </c>
       <c r="F11">
-        <v>32.913</v>
+        <v>36.56999999999999</v>
       </c>
       <c r="G11">
         <v>8.51</v>
@@ -2320,28 +2320,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M11">
-        <v>1.6555239</v>
+        <v>1.839471</v>
       </c>
       <c r="N11">
-        <v>48.56780943333333</v>
+        <v>48.38386233333333</v>
       </c>
       <c r="O11">
-        <v>9.713561886666668</v>
+        <v>9.676772466666666</v>
       </c>
       <c r="P11">
-        <v>38.85424754666666</v>
+        <v>38.70708986666666</v>
       </c>
       <c r="Q11">
-        <v>46.36424754666666</v>
+        <v>46.21708986666666</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07610635341760431</v>
+        <v>0.07638068112448465</v>
       </c>
       <c r="T11">
-        <v>0.5749003254415243</v>
+        <v>0.5801042206706849</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.33682167520103</v>
+        <v>27.30313950768092</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07276661301203619</v>
+        <v>0.07265484441405243</v>
       </c>
       <c r="C12">
-        <v>345.7054680666826</v>
+        <v>343.6040623459292</v>
       </c>
       <c r="D12">
-        <v>373.7654680666826</v>
+        <v>375.3210623459291</v>
       </c>
       <c r="E12">
-        <v>-82.53</v>
+        <v>-78.87299999999999</v>
       </c>
       <c r="F12">
-        <v>36.57</v>
+        <v>40.227</v>
       </c>
       <c r="G12">
         <v>8.51</v>
@@ -2402,28 +2402,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M12">
-        <v>1.839471</v>
+        <v>2.0234181</v>
       </c>
       <c r="N12">
-        <v>48.38386233333333</v>
+        <v>48.19991523333333</v>
       </c>
       <c r="O12">
-        <v>9.676772466666666</v>
+        <v>9.639983046666666</v>
       </c>
       <c r="P12">
-        <v>38.70708986666666</v>
+        <v>38.55993218666666</v>
       </c>
       <c r="Q12">
-        <v>46.21708986666666</v>
+        <v>46.06993218666666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07638068112448465</v>
+        <v>0.07666117349893531</v>
       </c>
       <c r="T12">
-        <v>0.580104220670685</v>
+        <v>0.5854250573656694</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.30313950768092</v>
+        <v>24.82103591607357</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07265484441405243</v>
+        <v>0.07254307581606868</v>
       </c>
       <c r="C13">
-        <v>343.6040623459292</v>
+        <v>341.5156593622443</v>
       </c>
       <c r="D13">
-        <v>375.3210623459291</v>
+        <v>376.8896593622443</v>
       </c>
       <c r="E13">
-        <v>-78.87299999999999</v>
+        <v>-75.21599999999999</v>
       </c>
       <c r="F13">
-        <v>40.227</v>
+        <v>43.884</v>
       </c>
       <c r="G13">
         <v>8.51</v>
@@ -2484,28 +2484,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M13">
-        <v>2.0234181</v>
+        <v>2.2073652</v>
       </c>
       <c r="N13">
-        <v>48.19991523333333</v>
+        <v>48.01596813333333</v>
       </c>
       <c r="O13">
-        <v>9.639983046666666</v>
+        <v>9.603193626666666</v>
       </c>
       <c r="P13">
-        <v>38.55993218666666</v>
+        <v>38.41277450666666</v>
       </c>
       <c r="Q13">
-        <v>46.06993218666666</v>
+        <v>45.92277450666666</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07666117349893531</v>
+        <v>0.07694804070007806</v>
       </c>
       <c r="T13">
-        <v>0.5854250573656694</v>
+        <v>0.5908668221673582</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.82103591607357</v>
+        <v>22.75261625640077</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07254307581606868</v>
+        <v>0.07243130721808494</v>
       </c>
       <c r="C14">
-        <v>341.5156593622443</v>
+        <v>339.4404228286986</v>
       </c>
       <c r="D14">
-        <v>376.8896593622443</v>
+        <v>378.4714228286986</v>
       </c>
       <c r="E14">
-        <v>-75.21599999999999</v>
+        <v>-71.559</v>
       </c>
       <c r="F14">
-        <v>43.884</v>
+        <v>47.541</v>
       </c>
       <c r="G14">
         <v>8.51</v>
@@ -2566,28 +2566,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M14">
-        <v>2.2073652</v>
+        <v>2.3913123</v>
       </c>
       <c r="N14">
-        <v>48.01596813333333</v>
+        <v>47.83202103333333</v>
       </c>
       <c r="O14">
-        <v>9.603193626666666</v>
+        <v>9.566404206666666</v>
       </c>
       <c r="P14">
-        <v>38.41277450666666</v>
+        <v>38.26561682666666</v>
       </c>
       <c r="Q14">
-        <v>45.92277450666666</v>
+        <v>45.77561682666666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07694804070007806</v>
+        <v>0.07724150254952292</v>
       </c>
       <c r="T14">
-        <v>0.5908668221673582</v>
+        <v>0.596433685010465</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.75261625640077</v>
+        <v>21.0024150059084</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07243130721808494</v>
+        <v>0.0723195386201012</v>
       </c>
       <c r="C15">
-        <v>339.4404228286986</v>
+        <v>337.3785192182871</v>
       </c>
       <c r="D15">
-        <v>378.4714228286986</v>
+        <v>380.0665192182871</v>
       </c>
       <c r="E15">
-        <v>-71.559</v>
+        <v>-67.90199999999999</v>
       </c>
       <c r="F15">
-        <v>47.541</v>
+        <v>51.198</v>
       </c>
       <c r="G15">
         <v>8.51</v>
@@ -2648,28 +2648,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M15">
-        <v>2.3913123</v>
+        <v>2.5752594</v>
       </c>
       <c r="N15">
-        <v>47.83202103333333</v>
+        <v>47.64807393333333</v>
       </c>
       <c r="O15">
-        <v>9.566404206666666</v>
+        <v>9.529614786666667</v>
       </c>
       <c r="P15">
-        <v>38.26561682666666</v>
+        <v>38.11845914666667</v>
       </c>
       <c r="Q15">
-        <v>45.77561682666666</v>
+        <v>45.62845914666666</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07724150254952292</v>
+        <v>0.07754178909314093</v>
       </c>
       <c r="T15">
-        <v>0.596433685010465</v>
+        <v>0.6021300097801557</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.0024150059084</v>
+        <v>19.50224250548637</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0723195386201012</v>
+        <v>0.07220777002211745</v>
       </c>
       <c r="C16">
-        <v>337.3785192182871</v>
+        <v>335.3301178223347</v>
       </c>
       <c r="D16">
-        <v>380.0665192182871</v>
+        <v>381.6751178223348</v>
       </c>
       <c r="E16">
-        <v>-67.90199999999999</v>
+        <v>-64.24499999999999</v>
       </c>
       <c r="F16">
-        <v>51.198</v>
+        <v>54.855</v>
       </c>
       <c r="G16">
         <v>8.51</v>
@@ -2730,28 +2730,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M16">
-        <v>2.5752594</v>
+        <v>2.7592065</v>
       </c>
       <c r="N16">
-        <v>47.64807393333333</v>
+        <v>47.46412683333333</v>
       </c>
       <c r="O16">
-        <v>9.529614786666667</v>
+        <v>9.492825366666667</v>
       </c>
       <c r="P16">
-        <v>38.11845914666667</v>
+        <v>37.97130146666667</v>
       </c>
       <c r="Q16">
-        <v>45.62845914666666</v>
+        <v>45.48130146666666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07754178909314093</v>
+        <v>0.07784914120249112</v>
       </c>
       <c r="T16">
-        <v>0.6021300097801557</v>
+        <v>0.607960365720898</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.50224250548637</v>
+        <v>18.20209300512061</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07220777002211745</v>
+        <v>0.07209600142413369</v>
       </c>
       <c r="C17">
-        <v>335.3301178223347</v>
+        <v>333.2953908103921</v>
       </c>
       <c r="D17">
-        <v>381.6751178223348</v>
+        <v>383.2973908103921</v>
       </c>
       <c r="E17">
-        <v>-64.245</v>
+        <v>-60.58799999999999</v>
       </c>
       <c r="F17">
-        <v>54.855</v>
+        <v>58.512</v>
       </c>
       <c r="G17">
         <v>8.51</v>
@@ -2812,28 +2812,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M17">
-        <v>2.7592065</v>
+        <v>2.9431536</v>
       </c>
       <c r="N17">
-        <v>47.46412683333333</v>
+        <v>47.28017973333333</v>
       </c>
       <c r="O17">
-        <v>9.492825366666667</v>
+        <v>9.456035946666665</v>
       </c>
       <c r="P17">
-        <v>37.97130146666667</v>
+        <v>37.82414378666666</v>
       </c>
       <c r="Q17">
-        <v>45.48130146666666</v>
+        <v>45.33414378666666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07784914120249112</v>
+        <v>0.07816381121920679</v>
       </c>
       <c r="T17">
-        <v>0.607960365720898</v>
+        <v>0.6139295396602292</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.20209300512061</v>
+        <v>17.06446219230057</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07209600142413369</v>
+        <v>0.07198423282614995</v>
       </c>
       <c r="C18">
-        <v>333.2953908103921</v>
+        <v>331.2745132916633</v>
       </c>
       <c r="D18">
-        <v>383.2973908103921</v>
+        <v>384.9335132916632</v>
       </c>
       <c r="E18">
-        <v>-60.58799999999999</v>
+        <v>-56.93099999999999</v>
       </c>
       <c r="F18">
-        <v>58.512</v>
+        <v>62.169</v>
       </c>
       <c r="G18">
         <v>8.51</v>
@@ -2894,28 +2894,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M18">
-        <v>2.9431536</v>
+        <v>3.1271007</v>
       </c>
       <c r="N18">
-        <v>47.28017973333333</v>
+        <v>47.09623263333333</v>
       </c>
       <c r="O18">
-        <v>9.456035946666665</v>
+        <v>9.419246526666667</v>
       </c>
       <c r="P18">
-        <v>37.82414378666666</v>
+        <v>37.67698610666666</v>
       </c>
       <c r="Q18">
-        <v>45.33414378666666</v>
+        <v>45.18698610666666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07816381121920679</v>
+        <v>0.07848606364596381</v>
       </c>
       <c r="T18">
-        <v>0.6139295396602292</v>
+        <v>0.6200425491161711</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.06446219230057</v>
+        <v>16.06067029863583</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07198423282614995</v>
+        <v>0.07187246422816621</v>
       </c>
       <c r="C19">
-        <v>331.2745132916633</v>
+        <v>329.2676633780171</v>
       </c>
       <c r="D19">
-        <v>384.9335132916632</v>
+        <v>386.5836633780171</v>
       </c>
       <c r="E19">
-        <v>-56.93099999999999</v>
+        <v>-53.27399999999999</v>
       </c>
       <c r="F19">
-        <v>62.169</v>
+        <v>65.82600000000001</v>
       </c>
       <c r="G19">
         <v>8.51</v>
@@ -2976,28 +2976,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M19">
-        <v>3.1271007</v>
+        <v>3.3110478</v>
       </c>
       <c r="N19">
-        <v>47.09623263333333</v>
+        <v>46.91228553333333</v>
       </c>
       <c r="O19">
-        <v>9.419246526666667</v>
+        <v>9.382457106666667</v>
       </c>
       <c r="P19">
-        <v>37.67698610666666</v>
+        <v>37.52982842666667</v>
       </c>
       <c r="Q19">
-        <v>45.18698610666666</v>
+        <v>45.03982842666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07848606364596381</v>
+        <v>0.07881617588800757</v>
       </c>
       <c r="T19">
-        <v>0.6200425491161711</v>
+        <v>0.6263046563637212</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.06067029863583</v>
+        <v>15.16841083760051</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07187246422816622</v>
+        <v>0.07176069563018247</v>
       </c>
       <c r="C20">
-        <v>329.267663378017</v>
+        <v>327.2750222486223</v>
       </c>
       <c r="D20">
-        <v>386.583663378017</v>
+        <v>388.2480222486223</v>
       </c>
       <c r="E20">
-        <v>-53.274</v>
+        <v>-49.61699999999999</v>
       </c>
       <c r="F20">
-        <v>65.82599999999999</v>
+        <v>69.483</v>
       </c>
       <c r="G20">
         <v>8.51</v>
@@ -3058,28 +3058,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M20">
-        <v>3.311047799999999</v>
+        <v>3.4949949</v>
       </c>
       <c r="N20">
-        <v>46.91228553333333</v>
+        <v>46.72833843333333</v>
       </c>
       <c r="O20">
-        <v>9.382457106666667</v>
+        <v>9.345667686666665</v>
       </c>
       <c r="P20">
-        <v>37.52982842666667</v>
+        <v>37.38267074666666</v>
       </c>
       <c r="Q20">
-        <v>45.03982842666667</v>
+        <v>44.89267074666666</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07881617588800757</v>
+        <v>0.07915443904960798</v>
       </c>
       <c r="T20">
-        <v>0.6263046563637211</v>
+        <v>0.6327213835433095</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.16841083760051</v>
+        <v>14.37007342509522</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07176069563018247</v>
+        <v>0.0716489270321987</v>
       </c>
       <c r="C21">
-        <v>327.2750222486223</v>
+        <v>325.2967742162629</v>
       </c>
       <c r="D21">
-        <v>388.2480222486223</v>
+        <v>389.9267742162629</v>
       </c>
       <c r="E21">
-        <v>-49.61699999999999</v>
+        <v>-45.95999999999999</v>
       </c>
       <c r="F21">
-        <v>69.483</v>
+        <v>73.14</v>
       </c>
       <c r="G21">
         <v>8.51</v>
@@ -3140,28 +3140,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M21">
-        <v>3.4949949</v>
+        <v>3.678942</v>
       </c>
       <c r="N21">
-        <v>46.72833843333333</v>
+        <v>46.54439133333333</v>
       </c>
       <c r="O21">
-        <v>9.345667686666665</v>
+        <v>9.308878266666666</v>
       </c>
       <c r="P21">
-        <v>37.38267074666666</v>
+        <v>37.23551306666666</v>
       </c>
       <c r="Q21">
-        <v>44.89267074666666</v>
+        <v>44.74551306666666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07915443904960798</v>
+        <v>0.07950115879024838</v>
       </c>
       <c r="T21">
-        <v>0.6327213835433095</v>
+        <v>0.6392985289023875</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.37007342509522</v>
+        <v>13.65156975384046</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0716489270321987</v>
+        <v>0.07153715843421496</v>
       </c>
       <c r="C22">
-        <v>325.2967742162629</v>
+        <v>323.3331067953769</v>
       </c>
       <c r="D22">
-        <v>389.9267742162629</v>
+        <v>391.620106795377</v>
       </c>
       <c r="E22">
-        <v>-45.95999999999999</v>
+        <v>-42.30299999999998</v>
       </c>
       <c r="F22">
-        <v>73.14</v>
+        <v>76.79700000000001</v>
       </c>
       <c r="G22">
         <v>8.51</v>
@@ -3222,28 +3222,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M22">
-        <v>3.678942</v>
+        <v>3.8628891</v>
       </c>
       <c r="N22">
-        <v>46.54439133333333</v>
+        <v>46.36044423333333</v>
       </c>
       <c r="O22">
-        <v>9.308878266666666</v>
+        <v>9.272088846666666</v>
       </c>
       <c r="P22">
-        <v>37.23551306666666</v>
+        <v>37.08835538666666</v>
       </c>
       <c r="Q22">
-        <v>44.74551306666666</v>
+        <v>44.59835538666666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07950115879024838</v>
+        <v>0.07985665624584172</v>
       </c>
       <c r="T22">
-        <v>0.6392985289023875</v>
+        <v>0.6460421842705562</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.65156975384046</v>
+        <v>13.00149500365758</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07153715843421496</v>
+        <v>0.07168938983623122</v>
       </c>
       <c r="C23">
-        <v>323.3331067953769</v>
+        <v>317.3733534940308</v>
       </c>
       <c r="D23">
-        <v>391.620106795377</v>
+        <v>389.3173534940308</v>
       </c>
       <c r="E23">
-        <v>-42.303</v>
+        <v>-38.646</v>
       </c>
       <c r="F23">
-        <v>76.797</v>
+        <v>80.45399999999999</v>
       </c>
       <c r="G23">
         <v>8.51</v>
@@ -3304,45 +3304,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M23">
-        <v>3.8628891</v>
+        <v>4.1675172</v>
       </c>
       <c r="N23">
-        <v>46.36044423333333</v>
+        <v>46.05581613333333</v>
       </c>
       <c r="O23">
-        <v>9.272088846666668</v>
+        <v>9.211163226666667</v>
       </c>
       <c r="P23">
-        <v>37.08835538666666</v>
+        <v>36.84465290666667</v>
       </c>
       <c r="Q23">
-        <v>44.59835538666666</v>
+        <v>44.35465290666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07985665624584172</v>
+        <v>0.08022126902080925</v>
       </c>
       <c r="T23">
-        <v>0.6460421842705562</v>
+        <v>0.6529587538789343</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.00149500365758</v>
+        <v>12.051140024889</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07168938983623122</v>
+        <v>0.07158962123824748</v>
       </c>
       <c r="C24">
-        <v>317.3733534940308</v>
+        <v>315.2224495382501</v>
       </c>
       <c r="D24">
-        <v>389.3173534940308</v>
+        <v>390.8234495382501</v>
       </c>
       <c r="E24">
-        <v>-38.646</v>
+        <v>-34.98899999999999</v>
       </c>
       <c r="F24">
-        <v>80.45399999999999</v>
+        <v>84.111</v>
       </c>
       <c r="G24">
         <v>8.51</v>
@@ -3386,28 +3386,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M24">
-        <v>4.1675172</v>
+        <v>4.3569498</v>
       </c>
       <c r="N24">
-        <v>46.05581613333333</v>
+        <v>45.86638353333333</v>
       </c>
       <c r="O24">
-        <v>9.211163226666667</v>
+        <v>9.173276706666666</v>
       </c>
       <c r="P24">
-        <v>36.84465290666667</v>
+        <v>36.69310682666666</v>
       </c>
       <c r="Q24">
-        <v>44.35465290666667</v>
+        <v>44.20310682666666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08022126902080925</v>
+        <v>0.08059535225746425</v>
       </c>
       <c r="T24">
-        <v>0.6529587538789343</v>
+        <v>0.6600549746459716</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.051140024889</v>
+        <v>11.52717741511122</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07158962123824748</v>
+        <v>0.07148985264026374</v>
       </c>
       <c r="C25">
-        <v>315.2224495382501</v>
+        <v>313.0832436714281</v>
       </c>
       <c r="D25">
-        <v>390.8234495382501</v>
+        <v>392.3412436714282</v>
       </c>
       <c r="E25">
-        <v>-34.98899999999999</v>
+        <v>-31.33199999999999</v>
       </c>
       <c r="F25">
-        <v>84.111</v>
+        <v>87.768</v>
       </c>
       <c r="G25">
         <v>8.51</v>
@@ -3468,28 +3468,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M25">
-        <v>4.3569498</v>
+        <v>4.5463824</v>
       </c>
       <c r="N25">
-        <v>45.86638353333333</v>
+        <v>45.67695093333333</v>
       </c>
       <c r="O25">
-        <v>9.173276706666666</v>
+        <v>9.135390186666667</v>
       </c>
       <c r="P25">
-        <v>36.69310682666666</v>
+        <v>36.54156074666666</v>
       </c>
       <c r="Q25">
-        <v>44.20310682666666</v>
+        <v>44.05156074666666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08059535225746425</v>
+        <v>0.0809792797898207</v>
       </c>
       <c r="T25">
-        <v>0.6600549746459716</v>
+        <v>0.667337938064773</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.52717741511122</v>
+        <v>11.04687835614825</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07148985264026372</v>
+        <v>0.07139008404227998</v>
       </c>
       <c r="C26">
-        <v>313.0832436714284</v>
+        <v>310.9558727163204</v>
       </c>
       <c r="D26">
-        <v>392.3412436714284</v>
+        <v>393.8708727163204</v>
       </c>
       <c r="E26">
-        <v>-31.33199999999999</v>
+        <v>-27.675</v>
       </c>
       <c r="F26">
-        <v>87.768</v>
+        <v>91.425</v>
       </c>
       <c r="G26">
         <v>8.51</v>
@@ -3550,28 +3550,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M26">
-        <v>4.5463824</v>
+        <v>4.735815</v>
       </c>
       <c r="N26">
-        <v>45.67695093333333</v>
+        <v>45.48751833333333</v>
       </c>
       <c r="O26">
-        <v>9.135390186666667</v>
+        <v>9.097503666666666</v>
       </c>
       <c r="P26">
-        <v>36.54156074666666</v>
+        <v>36.39001466666666</v>
       </c>
       <c r="Q26">
-        <v>44.05156074666666</v>
+        <v>43.90001466666666</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08097927978982068</v>
+        <v>0.08137344538970663</v>
       </c>
       <c r="T26">
-        <v>0.6673379380647729</v>
+        <v>0.674815113841409</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.04687835614825</v>
+        <v>10.60500322190232</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07139008404227998</v>
+        <v>0.07129031544429622</v>
       </c>
       <c r="C27">
-        <v>310.9558727163204</v>
+        <v>308.840475637768</v>
       </c>
       <c r="D27">
-        <v>393.8708727163204</v>
+        <v>395.412475637768</v>
       </c>
       <c r="E27">
-        <v>-27.675</v>
+        <v>-24.018</v>
       </c>
       <c r="F27">
-        <v>91.425</v>
+        <v>95.08199999999999</v>
       </c>
       <c r="G27">
         <v>8.51</v>
@@ -3632,28 +3632,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M27">
-        <v>4.735815</v>
+        <v>4.9252476</v>
       </c>
       <c r="N27">
-        <v>45.48751833333333</v>
+        <v>45.29808573333333</v>
       </c>
       <c r="O27">
-        <v>9.097503666666666</v>
+        <v>9.059617146666666</v>
       </c>
       <c r="P27">
-        <v>36.39001466666666</v>
+        <v>36.23846858666666</v>
       </c>
       <c r="Q27">
-        <v>43.90001466666666</v>
+        <v>43.74846858666666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08137344538970663</v>
+        <v>0.08177826411391381</v>
       </c>
       <c r="T27">
-        <v>0.674815113841409</v>
+        <v>0.6824943754498461</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.60500322190232</v>
+        <v>10.19711848259838</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07129031544429622</v>
+        <v>0.07119054684631247</v>
       </c>
       <c r="C28">
-        <v>308.840475637768</v>
+        <v>306.7371935847838</v>
       </c>
       <c r="D28">
-        <v>395.412475637768</v>
+        <v>396.9661935847838</v>
       </c>
       <c r="E28">
-        <v>-24.018</v>
+        <v>-20.36099999999999</v>
       </c>
       <c r="F28">
-        <v>95.08199999999999</v>
+        <v>98.739</v>
       </c>
       <c r="G28">
         <v>8.51</v>
@@ -3714,28 +3714,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M28">
-        <v>4.9252476</v>
+        <v>5.1146802</v>
       </c>
       <c r="N28">
-        <v>45.29808573333333</v>
+        <v>45.10865313333333</v>
       </c>
       <c r="O28">
-        <v>9.059617146666666</v>
+        <v>9.021730626666665</v>
       </c>
       <c r="P28">
-        <v>36.23846858666666</v>
+        <v>36.08692250666666</v>
       </c>
       <c r="Q28">
-        <v>43.74846858666666</v>
+        <v>43.59692250666666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08177826411391381</v>
+        <v>0.08219417376207189</v>
       </c>
       <c r="T28">
-        <v>0.6824943754498461</v>
+        <v>0.6903840277872816</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.19711848259838</v>
+        <v>9.819447427687331</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07119054684631247</v>
+        <v>0.07147157824832873</v>
       </c>
       <c r="C29">
-        <v>306.7371935847838</v>
+        <v>298.7345329924729</v>
       </c>
       <c r="D29">
-        <v>396.9661935847838</v>
+        <v>392.6205329924729</v>
       </c>
       <c r="E29">
-        <v>-20.36099999999999</v>
+        <v>-16.70399999999999</v>
       </c>
       <c r="F29">
-        <v>98.739</v>
+        <v>102.396</v>
       </c>
       <c r="G29">
         <v>8.51</v>
@@ -3796,45 +3796,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M29">
-        <v>5.1146802</v>
+        <v>5.478186</v>
       </c>
       <c r="N29">
-        <v>45.10865313333333</v>
+        <v>44.74514733333333</v>
       </c>
       <c r="O29">
-        <v>9.021730626666665</v>
+        <v>8.949029466666666</v>
       </c>
       <c r="P29">
-        <v>36.08692250666666</v>
+        <v>35.79611786666666</v>
       </c>
       <c r="Q29">
-        <v>43.59692250666666</v>
+        <v>43.30611786666666</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08219417376207189</v>
+        <v>0.08262163645601212</v>
       </c>
       <c r="T29">
-        <v>0.6903840277872816</v>
+        <v>0.69849283713409</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.819447427687331</v>
+        <v>9.167876617065088</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07147157824832873</v>
+        <v>0.07138540965034498</v>
       </c>
       <c r="C30">
-        <v>298.7345329924729</v>
+        <v>296.3998319640328</v>
       </c>
       <c r="D30">
-        <v>392.6205329924729</v>
+        <v>393.9428319640328</v>
       </c>
       <c r="E30">
-        <v>-16.70399999999999</v>
+        <v>-13.04699999999998</v>
       </c>
       <c r="F30">
-        <v>102.396</v>
+        <v>106.053</v>
       </c>
       <c r="G30">
         <v>8.51</v>
@@ -3878,28 +3878,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M30">
-        <v>5.478186</v>
+        <v>5.673835500000001</v>
       </c>
       <c r="N30">
-        <v>44.74514733333333</v>
+        <v>44.54949783333333</v>
       </c>
       <c r="O30">
-        <v>8.949029466666666</v>
+        <v>8.909899566666665</v>
       </c>
       <c r="P30">
-        <v>35.79611786666666</v>
+        <v>35.63959826666666</v>
       </c>
       <c r="Q30">
-        <v>43.30611786666666</v>
+        <v>43.14959826666666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08262163645601212</v>
+        <v>0.08306114035259857</v>
       </c>
       <c r="T30">
-        <v>0.69849283713409</v>
+        <v>0.7068300636455975</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.167876617065088</v>
+        <v>8.851742940614567</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07138540965034498</v>
+        <v>0.07129924105236124</v>
       </c>
       <c r="C31">
-        <v>296.3998319640328</v>
+        <v>294.0740677230258</v>
       </c>
       <c r="D31">
-        <v>393.9428319640328</v>
+        <v>395.2740677230258</v>
       </c>
       <c r="E31">
-        <v>-13.04700000000001</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="F31">
-        <v>106.053</v>
+        <v>109.71</v>
       </c>
       <c r="G31">
         <v>8.51</v>
@@ -3960,28 +3960,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M31">
-        <v>5.673835499999999</v>
+        <v>5.869484999999999</v>
       </c>
       <c r="N31">
-        <v>44.54949783333333</v>
+        <v>44.35384833333333</v>
       </c>
       <c r="O31">
-        <v>8.909899566666667</v>
+        <v>8.870769666666666</v>
       </c>
       <c r="P31">
-        <v>35.63959826666667</v>
+        <v>35.48307866666666</v>
       </c>
       <c r="Q31">
-        <v>43.14959826666666</v>
+        <v>42.99307866666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08306114035259857</v>
+        <v>0.0835132015033732</v>
       </c>
       <c r="T31">
-        <v>0.7068300636455975</v>
+        <v>0.7154054966288623</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.851742940614571</v>
+        <v>8.556684842594084</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07129924105236124</v>
+        <v>0.07121307245437748</v>
       </c>
       <c r="C32">
-        <v>294.0740677230258</v>
+        <v>291.7573311758679</v>
       </c>
       <c r="D32">
-        <v>395.2740677230258</v>
+        <v>396.6143311758679</v>
       </c>
       <c r="E32">
-        <v>-9.390000000000001</v>
+        <v>-5.733000000000004</v>
       </c>
       <c r="F32">
-        <v>109.71</v>
+        <v>113.367</v>
       </c>
       <c r="G32">
         <v>8.51</v>
@@ -4042,28 +4042,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M32">
-        <v>5.869484999999999</v>
+        <v>6.065134499999999</v>
       </c>
       <c r="N32">
-        <v>44.35384833333333</v>
+        <v>44.15819883333333</v>
       </c>
       <c r="O32">
-        <v>8.870769666666666</v>
+        <v>8.831639766666667</v>
       </c>
       <c r="P32">
-        <v>35.48307866666666</v>
+        <v>35.32655906666666</v>
       </c>
       <c r="Q32">
-        <v>42.99307866666666</v>
+        <v>42.83655906666666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0835132015033732</v>
+        <v>0.0839783658759094</v>
       </c>
       <c r="T32">
-        <v>0.7154054966288623</v>
+        <v>0.7242294928870042</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.556684842594084</v>
+        <v>8.2806627508975</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07121307245437748</v>
+        <v>0.07112690385639374</v>
       </c>
       <c r="C33">
-        <v>291.7573311758679</v>
+        <v>289.4497144661219</v>
       </c>
       <c r="D33">
-        <v>396.6143311758679</v>
+        <v>397.9637144661219</v>
       </c>
       <c r="E33">
-        <v>-5.733000000000004</v>
+        <v>-2.075999999999993</v>
       </c>
       <c r="F33">
-        <v>113.367</v>
+        <v>117.024</v>
       </c>
       <c r="G33">
         <v>8.51</v>
@@ -4124,28 +4124,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M33">
-        <v>6.065134499999999</v>
+        <v>6.260784</v>
       </c>
       <c r="N33">
-        <v>44.15819883333333</v>
+        <v>43.96254933333333</v>
       </c>
       <c r="O33">
-        <v>8.831639766666667</v>
+        <v>8.792509866666666</v>
       </c>
       <c r="P33">
-        <v>35.32655906666666</v>
+        <v>35.17003946666667</v>
       </c>
       <c r="Q33">
-        <v>42.83655906666666</v>
+        <v>42.68003946666666</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0839783658759094</v>
+        <v>0.08445721155352021</v>
       </c>
       <c r="T33">
-        <v>0.7242294928870042</v>
+        <v>0.7333130184468563</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.2806627508975</v>
+        <v>8.021892039931952</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07112690385639374</v>
+        <v>0.07104073525841</v>
       </c>
       <c r="C34">
-        <v>289.4497144661219</v>
+        <v>287.1513109956156</v>
       </c>
       <c r="D34">
-        <v>397.9637144661219</v>
+        <v>399.3223109956156</v>
       </c>
       <c r="E34">
-        <v>-2.075999999999993</v>
+        <v>1.581000000000003</v>
       </c>
       <c r="F34">
-        <v>117.024</v>
+        <v>120.681</v>
       </c>
       <c r="G34">
         <v>8.51</v>
@@ -4206,28 +4206,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M34">
-        <v>6.260784</v>
+        <v>6.4564335</v>
       </c>
       <c r="N34">
-        <v>43.96254933333333</v>
+        <v>43.76689983333333</v>
       </c>
       <c r="O34">
-        <v>8.792509866666666</v>
+        <v>8.753379966666666</v>
       </c>
       <c r="P34">
-        <v>35.17003946666667</v>
+        <v>35.01351986666666</v>
       </c>
       <c r="Q34">
-        <v>42.68003946666666</v>
+        <v>42.52351986666666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08445721155352021</v>
+        <v>0.08495035113195522</v>
       </c>
       <c r="T34">
-        <v>0.7333130184468563</v>
+        <v>0.7426676940234204</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.021892039931952</v>
+        <v>7.778804402358256</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07104073525841</v>
+        <v>0.07117216666042625</v>
       </c>
       <c r="C35">
-        <v>287.1513109956156</v>
+        <v>281.4257651007006</v>
       </c>
       <c r="D35">
-        <v>399.3223109956156</v>
+        <v>397.2537651007007</v>
       </c>
       <c r="E35">
-        <v>1.581000000000003</v>
+        <v>5.238000000000014</v>
       </c>
       <c r="F35">
-        <v>120.681</v>
+        <v>124.338</v>
       </c>
       <c r="G35">
         <v>8.51</v>
@@ -4288,45 +4288,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M35">
-        <v>6.4564335</v>
+        <v>6.751553400000001</v>
       </c>
       <c r="N35">
-        <v>43.76689983333333</v>
+        <v>43.47177993333333</v>
       </c>
       <c r="O35">
-        <v>8.753379966666666</v>
+        <v>8.694355986666666</v>
       </c>
       <c r="P35">
-        <v>35.01351986666666</v>
+        <v>34.77742394666667</v>
       </c>
       <c r="Q35">
-        <v>42.52351986666666</v>
+        <v>42.28742394666666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08495035113195522</v>
+        <v>0.08545843433397916</v>
       </c>
       <c r="T35">
-        <v>0.7426676940234204</v>
+        <v>0.7523058446174561</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.778804402358256</v>
+        <v>7.438781915482343</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07117216666042625</v>
+        <v>0.0710923980624425</v>
       </c>
       <c r="C36">
-        <v>281.4257651007006</v>
+        <v>279.0216465320152</v>
       </c>
       <c r="D36">
-        <v>397.2537651007007</v>
+        <v>398.5066465320152</v>
       </c>
       <c r="E36">
-        <v>5.238000000000014</v>
+        <v>8.89500000000001</v>
       </c>
       <c r="F36">
-        <v>124.338</v>
+        <v>127.995</v>
       </c>
       <c r="G36">
         <v>8.51</v>
@@ -4370,28 +4370,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M36">
-        <v>6.751553400000001</v>
+        <v>6.950128500000001</v>
       </c>
       <c r="N36">
-        <v>43.47177993333333</v>
+        <v>43.27320483333333</v>
       </c>
       <c r="O36">
-        <v>8.694355986666666</v>
+        <v>8.654640966666667</v>
       </c>
       <c r="P36">
-        <v>34.77742394666667</v>
+        <v>34.61856386666666</v>
       </c>
       <c r="Q36">
-        <v>42.28742394666666</v>
+        <v>42.12856386666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08545843433397916</v>
+        <v>0.08598215086529615</v>
       </c>
       <c r="T36">
-        <v>0.7523058446174561</v>
+        <v>0.7622405536913083</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.438781915482343</v>
+        <v>7.226245289325704</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0710923980624425</v>
+        <v>0.07101262946445874</v>
       </c>
       <c r="C37">
-        <v>279.0216465320152</v>
+        <v>276.6254557834213</v>
       </c>
       <c r="D37">
-        <v>398.5066465320152</v>
+        <v>399.7674557834214</v>
       </c>
       <c r="E37">
-        <v>8.89500000000001</v>
+        <v>12.55200000000002</v>
       </c>
       <c r="F37">
-        <v>127.995</v>
+        <v>131.652</v>
       </c>
       <c r="G37">
         <v>8.51</v>
@@ -4452,28 +4452,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M37">
-        <v>6.950128500000001</v>
+        <v>7.148703600000001</v>
       </c>
       <c r="N37">
-        <v>43.27320483333333</v>
+        <v>43.07462973333332</v>
       </c>
       <c r="O37">
-        <v>8.654640966666667</v>
+        <v>8.614925946666665</v>
       </c>
       <c r="P37">
-        <v>34.61856386666666</v>
+        <v>34.45970378666666</v>
       </c>
       <c r="Q37">
-        <v>42.12856386666666</v>
+        <v>41.96970378666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08598215086529615</v>
+        <v>0.08652223353821681</v>
       </c>
       <c r="T37">
-        <v>0.7622405536913083</v>
+        <v>0.7724857224237184</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.226245289325704</v>
+        <v>7.025516253511101</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07101262946445876</v>
+        <v>0.070932860866475</v>
       </c>
       <c r="C38">
-        <v>276.6254557834212</v>
+        <v>274.2372683406861</v>
       </c>
       <c r="D38">
-        <v>399.7674557834212</v>
+        <v>401.0362683406861</v>
       </c>
       <c r="E38">
-        <v>12.55199999999999</v>
+        <v>16.209</v>
       </c>
       <c r="F38">
-        <v>131.652</v>
+        <v>135.309</v>
       </c>
       <c r="G38">
         <v>8.51</v>
@@ -4534,28 +4534,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M38">
-        <v>7.148703599999999</v>
+        <v>7.3472787</v>
       </c>
       <c r="N38">
-        <v>43.07462973333333</v>
+        <v>42.87605463333333</v>
       </c>
       <c r="O38">
-        <v>8.614925946666666</v>
+        <v>8.575210926666665</v>
       </c>
       <c r="P38">
-        <v>34.45970378666667</v>
+        <v>34.30084370666666</v>
       </c>
       <c r="Q38">
-        <v>41.96970378666666</v>
+        <v>41.81084370666666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08652223353821681</v>
+        <v>0.08707946169281747</v>
       </c>
       <c r="T38">
-        <v>0.7724857224237183</v>
+        <v>0.783056134607951</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.025516253511103</v>
+        <v>6.835637435848639</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.070932860866475</v>
+        <v>0.07085309226849126</v>
       </c>
       <c r="C39">
-        <v>274.2372683406861</v>
+        <v>271.8571606509579</v>
       </c>
       <c r="D39">
-        <v>401.0362683406861</v>
+        <v>402.3131606509579</v>
       </c>
       <c r="E39">
-        <v>16.209</v>
+        <v>19.86600000000001</v>
       </c>
       <c r="F39">
-        <v>135.309</v>
+        <v>138.966</v>
       </c>
       <c r="G39">
         <v>8.51</v>
@@ -4616,28 +4616,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M39">
-        <v>7.3472787</v>
+        <v>7.545853800000001</v>
       </c>
       <c r="N39">
-        <v>42.87605463333333</v>
+        <v>42.67747953333333</v>
       </c>
       <c r="O39">
-        <v>8.575210926666665</v>
+        <v>8.535495906666666</v>
       </c>
       <c r="P39">
-        <v>34.30084370666666</v>
+        <v>34.14198362666666</v>
       </c>
       <c r="Q39">
-        <v>41.81084370666666</v>
+        <v>41.65198362666666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08707946169281747</v>
+        <v>0.08765466494917945</v>
       </c>
       <c r="T39">
-        <v>0.783056134607951</v>
+        <v>0.7939675278303845</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.835637435848639</v>
+        <v>6.655752240168412</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07085309226849126</v>
+        <v>0.07077332367050752</v>
       </c>
       <c r="C40">
-        <v>271.8571606509579</v>
+        <v>269.4852101381206</v>
       </c>
       <c r="D40">
-        <v>402.3131606509579</v>
+        <v>403.5982101381206</v>
       </c>
       <c r="E40">
-        <v>19.86600000000001</v>
+        <v>23.523</v>
       </c>
       <c r="F40">
-        <v>138.966</v>
+        <v>142.623</v>
       </c>
       <c r="G40">
         <v>8.51</v>
@@ -4698,28 +4698,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M40">
-        <v>7.545853800000001</v>
+        <v>7.7444289</v>
       </c>
       <c r="N40">
-        <v>42.67747953333333</v>
+        <v>42.47890443333333</v>
       </c>
       <c r="O40">
-        <v>8.535495906666666</v>
+        <v>8.495780886666665</v>
       </c>
       <c r="P40">
-        <v>34.14198362666666</v>
+        <v>33.98312354666666</v>
       </c>
       <c r="Q40">
-        <v>41.65198362666666</v>
+        <v>41.49312354666666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08765466494917945</v>
+        <v>0.08824872732870084</v>
       </c>
       <c r="T40">
-        <v>0.7939675278303845</v>
+        <v>0.805236671650275</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.655752240168412</v>
+        <v>6.48509192631794</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07077332367050752</v>
+        <v>0.07069355507252376</v>
       </c>
       <c r="C41">
-        <v>269.4852101381206</v>
+        <v>267.121495218443</v>
       </c>
       <c r="D41">
-        <v>403.5982101381206</v>
+        <v>404.891495218443</v>
       </c>
       <c r="E41">
-        <v>23.523</v>
+        <v>27.18000000000001</v>
       </c>
       <c r="F41">
-        <v>142.623</v>
+        <v>146.28</v>
       </c>
       <c r="G41">
         <v>8.51</v>
@@ -4780,28 +4780,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M41">
-        <v>7.7444289</v>
+        <v>7.943004</v>
       </c>
       <c r="N41">
-        <v>42.47890443333333</v>
+        <v>42.28032933333333</v>
       </c>
       <c r="O41">
-        <v>8.495780886666665</v>
+        <v>8.456065866666666</v>
       </c>
       <c r="P41">
-        <v>33.98312354666666</v>
+        <v>33.82426346666666</v>
       </c>
       <c r="Q41">
-        <v>41.49312354666666</v>
+        <v>41.33426346666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08824872732870084</v>
+        <v>0.08886259178753961</v>
       </c>
       <c r="T41">
-        <v>0.805236671650275</v>
+        <v>0.8168814535974952</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.48509192631794</v>
+        <v>6.322964628159991</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07069355507252376</v>
+        <v>0.07061378647454003</v>
       </c>
       <c r="C42">
-        <v>267.121495218443</v>
+        <v>264.7660953165275</v>
       </c>
       <c r="D42">
-        <v>404.891495218443</v>
+        <v>406.1930953165275</v>
       </c>
       <c r="E42">
-        <v>27.18000000000001</v>
+        <v>30.83700000000002</v>
       </c>
       <c r="F42">
-        <v>146.28</v>
+        <v>149.937</v>
       </c>
       <c r="G42">
         <v>8.51</v>
@@ -4862,28 +4862,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M42">
-        <v>7.943004</v>
+        <v>8.141579100000001</v>
       </c>
       <c r="N42">
-        <v>42.28032933333333</v>
+        <v>42.08175423333333</v>
       </c>
       <c r="O42">
-        <v>8.456065866666666</v>
+        <v>8.416350846666665</v>
       </c>
       <c r="P42">
-        <v>33.82426346666666</v>
+        <v>33.66540338666666</v>
       </c>
       <c r="Q42">
-        <v>41.33426346666666</v>
+        <v>41.17540338666666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08886259178753961</v>
+        <v>0.08949726521108478</v>
       </c>
       <c r="T42">
-        <v>0.8168814535974952</v>
+        <v>0.8289209739158077</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.322964628159991</v>
+        <v>6.168745978692674</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07061378647454003</v>
+        <v>0.07087001787655628</v>
       </c>
       <c r="C43">
-        <v>264.7660953165275</v>
+        <v>256.9575455723367</v>
       </c>
       <c r="D43">
-        <v>406.1930953165275</v>
+        <v>402.0415455723368</v>
       </c>
       <c r="E43">
-        <v>30.83700000000002</v>
+        <v>34.49400000000003</v>
       </c>
       <c r="F43">
-        <v>149.937</v>
+        <v>153.594</v>
       </c>
       <c r="G43">
         <v>8.51</v>
@@ -4944,45 +4944,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M43">
-        <v>8.141579100000001</v>
+        <v>8.493748200000002</v>
       </c>
       <c r="N43">
-        <v>42.08175423333333</v>
+        <v>41.72958513333333</v>
       </c>
       <c r="O43">
-        <v>8.416350846666665</v>
+        <v>8.345917026666667</v>
       </c>
       <c r="P43">
-        <v>33.66540338666666</v>
+        <v>33.38366810666666</v>
       </c>
       <c r="Q43">
-        <v>41.17540338666666</v>
+        <v>40.89366810666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08949726521108478</v>
+        <v>0.09015382392509702</v>
       </c>
       <c r="T43">
-        <v>0.8289209739158077</v>
+        <v>0.8413756501071653</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.168745978692674</v>
+        <v>5.912976479963619</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07087001787655628</v>
+        <v>0.07079824927857253</v>
       </c>
       <c r="C44">
-        <v>256.9575455723368</v>
+        <v>254.4547847246632</v>
       </c>
       <c r="D44">
-        <v>402.0415455723368</v>
+        <v>403.1957847246632</v>
       </c>
       <c r="E44">
-        <v>34.494</v>
+        <v>38.15100000000001</v>
       </c>
       <c r="F44">
-        <v>153.594</v>
+        <v>157.251</v>
       </c>
       <c r="G44">
         <v>8.51</v>
@@ -5026,28 +5026,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M44">
-        <v>8.493748200000001</v>
+        <v>8.6959803</v>
       </c>
       <c r="N44">
-        <v>41.72958513333333</v>
+        <v>41.52735303333333</v>
       </c>
       <c r="O44">
-        <v>8.345917026666667</v>
+        <v>8.305470606666665</v>
       </c>
       <c r="P44">
-        <v>33.38366810666666</v>
+        <v>33.22188242666666</v>
       </c>
       <c r="Q44">
-        <v>40.89366810666666</v>
+        <v>40.73188242666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09015382392509701</v>
+        <v>0.09083341978696934</v>
       </c>
       <c r="T44">
-        <v>0.8413756501071651</v>
+        <v>0.8542673324806758</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.91297647996362</v>
+        <v>5.775465399034233</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07079824927857253</v>
+        <v>0.07072648068058879</v>
       </c>
       <c r="C45">
-        <v>254.4547847246632</v>
+        <v>251.9586704731748</v>
       </c>
       <c r="D45">
-        <v>403.1957847246632</v>
+        <v>404.3566704731748</v>
       </c>
       <c r="E45">
-        <v>38.15100000000001</v>
+        <v>41.80799999999999</v>
       </c>
       <c r="F45">
-        <v>157.251</v>
+        <v>160.908</v>
       </c>
       <c r="G45">
         <v>8.51</v>
@@ -5108,28 +5108,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M45">
-        <v>8.6959803</v>
+        <v>8.8982124</v>
       </c>
       <c r="N45">
-        <v>41.52735303333333</v>
+        <v>41.32512093333333</v>
       </c>
       <c r="O45">
-        <v>8.305470606666665</v>
+        <v>8.265024186666666</v>
       </c>
       <c r="P45">
-        <v>33.22188242666666</v>
+        <v>33.06009674666667</v>
       </c>
       <c r="Q45">
-        <v>40.73188242666666</v>
+        <v>40.57009674666666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09083341978696934</v>
+        <v>0.09153728692962282</v>
       </c>
       <c r="T45">
-        <v>0.8542673324806758</v>
+        <v>0.8676194320818117</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.775465399034233</v>
+        <v>5.644204821783455</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07072648068058879</v>
+        <v>0.07065471208260504</v>
       </c>
       <c r="C46">
-        <v>251.9586704731748</v>
+        <v>249.4692603945059</v>
       </c>
       <c r="D46">
-        <v>404.3566704731748</v>
+        <v>405.5242603945059</v>
       </c>
       <c r="E46">
-        <v>41.80799999999999</v>
+        <v>45.465</v>
       </c>
       <c r="F46">
-        <v>160.908</v>
+        <v>164.565</v>
       </c>
       <c r="G46">
         <v>8.51</v>
@@ -5190,28 +5190,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M46">
-        <v>8.8982124</v>
+        <v>9.1004445</v>
       </c>
       <c r="N46">
-        <v>41.32512093333333</v>
+        <v>41.12288883333333</v>
       </c>
       <c r="O46">
-        <v>8.265024186666666</v>
+        <v>8.224577766666666</v>
       </c>
       <c r="P46">
-        <v>33.06009674666667</v>
+        <v>32.89831106666666</v>
       </c>
       <c r="Q46">
-        <v>40.57009674666666</v>
+        <v>40.40831106666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09153728692962282</v>
+        <v>0.09226674924110005</v>
       </c>
       <c r="T46">
-        <v>0.8676194320818117</v>
+        <v>0.8814570625775343</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.644204821783455</v>
+        <v>5.518778047966045</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07065471208260504</v>
+        <v>0.07058294348462128</v>
       </c>
       <c r="C47">
-        <v>249.4692603945059</v>
+        <v>246.9866127322325</v>
       </c>
       <c r="D47">
-        <v>405.5242603945059</v>
+        <v>406.6986127322326</v>
       </c>
       <c r="E47">
-        <v>45.465</v>
+        <v>49.12200000000001</v>
       </c>
       <c r="F47">
-        <v>164.565</v>
+        <v>168.222</v>
       </c>
       <c r="G47">
         <v>8.51</v>
@@ -5272,28 +5272,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M47">
-        <v>9.1004445</v>
+        <v>9.302676600000002</v>
       </c>
       <c r="N47">
-        <v>41.12288883333333</v>
+        <v>40.92065673333333</v>
       </c>
       <c r="O47">
-        <v>8.224577766666666</v>
+        <v>8.184131346666666</v>
       </c>
       <c r="P47">
-        <v>32.89831106666666</v>
+        <v>32.73652538666666</v>
       </c>
       <c r="Q47">
-        <v>40.40831106666666</v>
+        <v>40.24652538666666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09226674924110005</v>
+        <v>0.09302322867522458</v>
       </c>
       <c r="T47">
-        <v>0.8814570625775343</v>
+        <v>0.8958071979064319</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.518778047966045</v>
+        <v>5.398804612140696</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07058294348462128</v>
+        <v>0.07051117488663754</v>
       </c>
       <c r="C48">
-        <v>246.9866127322325</v>
+        <v>244.5107864065571</v>
       </c>
       <c r="D48">
-        <v>406.6986127322326</v>
+        <v>407.8797864065571</v>
       </c>
       <c r="E48">
-        <v>49.12200000000001</v>
+        <v>52.77900000000002</v>
       </c>
       <c r="F48">
-        <v>168.222</v>
+        <v>171.879</v>
       </c>
       <c r="G48">
         <v>8.51</v>
@@ -5354,28 +5354,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M48">
-        <v>9.302676600000002</v>
+        <v>9.504908700000001</v>
       </c>
       <c r="N48">
-        <v>40.92065673333333</v>
+        <v>40.71842463333333</v>
       </c>
       <c r="O48">
-        <v>8.184131346666666</v>
+        <v>8.143684926666666</v>
       </c>
       <c r="P48">
-        <v>32.73652538666666</v>
+        <v>32.57473970666666</v>
       </c>
       <c r="Q48">
-        <v>40.24652538666666</v>
+        <v>40.08473970666666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09302322867522458</v>
+        <v>0.09380825450308969</v>
       </c>
       <c r="T48">
-        <v>0.8958071979064319</v>
+        <v>0.9106988477760427</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.398804612140696</v>
+        <v>5.283936428903659</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07051117488663754</v>
+        <v>0.07043940628865379</v>
       </c>
       <c r="C49">
-        <v>244.5107864065571</v>
+        <v>242.0418410241633</v>
       </c>
       <c r="D49">
-        <v>407.8797864065571</v>
+        <v>409.0678410241633</v>
       </c>
       <c r="E49">
-        <v>52.77900000000002</v>
+        <v>56.43600000000001</v>
       </c>
       <c r="F49">
-        <v>171.879</v>
+        <v>175.536</v>
       </c>
       <c r="G49">
         <v>8.51</v>
@@ -5436,28 +5436,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M49">
-        <v>9.504908700000001</v>
+        <v>9.707140800000001</v>
       </c>
       <c r="N49">
-        <v>40.71842463333333</v>
+        <v>40.51619253333332</v>
       </c>
       <c r="O49">
-        <v>8.143684926666666</v>
+        <v>8.103238506666665</v>
       </c>
       <c r="P49">
-        <v>32.57473970666666</v>
+        <v>32.41295402666666</v>
       </c>
       <c r="Q49">
-        <v>40.08473970666666</v>
+        <v>39.92295402666666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09380825450308969</v>
+        <v>0.09462347363202651</v>
       </c>
       <c r="T49">
-        <v>0.9106988477760427</v>
+        <v>0.9261632534098692</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.283936428903659</v>
+        <v>5.173854419968166</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07043940628865379</v>
+        <v>0.07036763769067003</v>
       </c>
       <c r="C50">
-        <v>242.0418410241633</v>
+        <v>239.5798368882425</v>
       </c>
       <c r="D50">
-        <v>409.0678410241633</v>
+        <v>410.2628368882425</v>
       </c>
       <c r="E50">
-        <v>56.43600000000001</v>
+        <v>60.09299999999999</v>
       </c>
       <c r="F50">
-        <v>175.536</v>
+        <v>179.193</v>
       </c>
       <c r="G50">
         <v>8.51</v>
@@ -5518,28 +5518,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M50">
-        <v>9.707140800000001</v>
+        <v>9.909372899999999</v>
       </c>
       <c r="N50">
-        <v>40.51619253333332</v>
+        <v>40.31396043333333</v>
       </c>
       <c r="O50">
-        <v>8.103238506666665</v>
+        <v>8.062792086666667</v>
       </c>
       <c r="P50">
-        <v>32.41295402666666</v>
+        <v>32.25116834666666</v>
       </c>
       <c r="Q50">
-        <v>39.92295402666666</v>
+        <v>39.76116834666666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09462347363202651</v>
+        <v>0.0954706621385687</v>
       </c>
       <c r="T50">
-        <v>0.9261632534098692</v>
+        <v>0.9422341063234535</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.173854419968166</v>
+        <v>5.068265554254531</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07036763769067003</v>
+        <v>0.07029586909268629</v>
       </c>
       <c r="C51">
-        <v>239.5798368882425</v>
+        <v>237.1248350086968</v>
       </c>
       <c r="D51">
-        <v>410.2628368882425</v>
+        <v>411.4648350086968</v>
       </c>
       <c r="E51">
-        <v>60.09299999999999</v>
+        <v>63.75</v>
       </c>
       <c r="F51">
-        <v>179.193</v>
+        <v>182.85</v>
       </c>
       <c r="G51">
         <v>8.51</v>
@@ -5600,28 +5600,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M51">
-        <v>9.909372899999999</v>
+        <v>10.111605</v>
       </c>
       <c r="N51">
-        <v>40.31396043333333</v>
+        <v>40.11172833333333</v>
       </c>
       <c r="O51">
-        <v>8.062792086666667</v>
+        <v>8.022345666666666</v>
       </c>
       <c r="P51">
-        <v>32.25116834666666</v>
+        <v>32.08938266666667</v>
       </c>
       <c r="Q51">
-        <v>39.76116834666666</v>
+        <v>39.59938266666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0954706621385687</v>
+        <v>0.09635173818537258</v>
       </c>
       <c r="T51">
-        <v>0.9422341063234535</v>
+        <v>0.9589477933535814</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.068265554254531</v>
+        <v>4.966900243169441</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07029586909268629</v>
+        <v>0.07022410049470255</v>
       </c>
       <c r="C52">
-        <v>237.1248350086968</v>
+        <v>234.6768971125227</v>
       </c>
       <c r="D52">
-        <v>411.4648350086968</v>
+        <v>412.6738971125228</v>
       </c>
       <c r="E52">
-        <v>63.75</v>
+        <v>67.40700000000001</v>
       </c>
       <c r="F52">
-        <v>182.85</v>
+        <v>186.507</v>
       </c>
       <c r="G52">
         <v>8.51</v>
@@ -5682,28 +5682,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M52">
-        <v>10.111605</v>
+        <v>10.3138371</v>
       </c>
       <c r="N52">
-        <v>40.11172833333333</v>
+        <v>39.90949623333333</v>
       </c>
       <c r="O52">
-        <v>8.022345666666666</v>
+        <v>7.981899246666666</v>
       </c>
       <c r="P52">
-        <v>32.08938266666667</v>
+        <v>31.92759698666666</v>
       </c>
       <c r="Q52">
-        <v>39.59938266666666</v>
+        <v>39.43759698666666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09635173818537258</v>
+        <v>0.09726877651980112</v>
       </c>
       <c r="T52">
-        <v>0.9589477933535814</v>
+        <v>0.9763436716910614</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.966900243169441</v>
+        <v>4.869510042322981</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07022410049470255</v>
+        <v>0.07015233189671879</v>
       </c>
       <c r="C53">
-        <v>234.6768971125227</v>
+        <v>232.2360856543786</v>
       </c>
       <c r="D53">
-        <v>412.6738971125228</v>
+        <v>413.8900856543786</v>
       </c>
       <c r="E53">
-        <v>67.40700000000001</v>
+        <v>71.06399999999999</v>
       </c>
       <c r="F53">
-        <v>186.507</v>
+        <v>190.164</v>
       </c>
       <c r="G53">
         <v>8.51</v>
@@ -5764,28 +5764,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M53">
-        <v>10.3138371</v>
+        <v>10.5160692</v>
       </c>
       <c r="N53">
-        <v>39.90949623333333</v>
+        <v>39.70726413333333</v>
       </c>
       <c r="O53">
-        <v>7.981899246666666</v>
+        <v>7.941452826666666</v>
       </c>
       <c r="P53">
-        <v>31.92759698666666</v>
+        <v>31.76581130666666</v>
       </c>
       <c r="Q53">
-        <v>39.43759698666666</v>
+        <v>39.27581130666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09726877651980112</v>
+        <v>0.09822402478483083</v>
       </c>
       <c r="T53">
-        <v>0.9763436716910614</v>
+        <v>0.9944643782926028</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.869510042322981</v>
+        <v>4.775865618432153</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07015233189671879</v>
+        <v>0.07008056329873505</v>
       </c>
       <c r="C54">
-        <v>232.2360856543786</v>
+        <v>229.8024638273362</v>
       </c>
       <c r="D54">
-        <v>413.8900856543786</v>
+        <v>415.1134638273362</v>
       </c>
       <c r="E54">
-        <v>71.06399999999999</v>
+        <v>74.721</v>
       </c>
       <c r="F54">
-        <v>190.164</v>
+        <v>193.821</v>
       </c>
       <c r="G54">
         <v>8.51</v>
@@ -5846,28 +5846,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M54">
-        <v>10.5160692</v>
+        <v>10.7183013</v>
       </c>
       <c r="N54">
-        <v>39.70726413333333</v>
+        <v>39.50503203333333</v>
       </c>
       <c r="O54">
-        <v>7.941452826666666</v>
+        <v>7.901006406666666</v>
       </c>
       <c r="P54">
-        <v>31.76581130666666</v>
+        <v>31.60402562666666</v>
       </c>
       <c r="Q54">
-        <v>39.27581130666666</v>
+        <v>39.11402562666666</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09822402478483083</v>
+        <v>0.09921992191220223</v>
       </c>
       <c r="T54">
-        <v>0.9944643782926028</v>
+        <v>1.013356178792082</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.775865618432153</v>
+        <v>4.685754946386265</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07008056329873505</v>
+        <v>0.0700087947007513</v>
       </c>
       <c r="C55">
-        <v>229.8024638273362</v>
+        <v>227.3760955738286</v>
       </c>
       <c r="D55">
-        <v>415.1134638273362</v>
+        <v>416.3440955738287</v>
       </c>
       <c r="E55">
-        <v>74.721</v>
+        <v>78.37800000000001</v>
       </c>
       <c r="F55">
-        <v>193.821</v>
+        <v>197.478</v>
       </c>
       <c r="G55">
         <v>8.51</v>
@@ -5928,28 +5928,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M55">
-        <v>10.7183013</v>
+        <v>10.9205334</v>
       </c>
       <c r="N55">
-        <v>39.50503203333333</v>
+        <v>39.30279993333333</v>
       </c>
       <c r="O55">
-        <v>7.901006406666666</v>
+        <v>7.860559986666667</v>
       </c>
       <c r="P55">
-        <v>31.60402562666666</v>
+        <v>31.44223994666667</v>
       </c>
       <c r="Q55">
-        <v>39.11402562666666</v>
+        <v>38.95223994666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09921992191220223</v>
+        <v>0.1002591189146767</v>
       </c>
       <c r="T55">
-        <v>1.013356178792082</v>
+        <v>1.033069361921974</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.685754946386265</v>
+        <v>4.598981706638371</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0700087947007513</v>
+        <v>0.06993702610276756</v>
       </c>
       <c r="C56">
-        <v>227.3760955738286</v>
+        <v>224.9570455967902</v>
       </c>
       <c r="D56">
-        <v>416.3440955738287</v>
+        <v>417.5820455967902</v>
       </c>
       <c r="E56">
-        <v>78.37800000000001</v>
+        <v>82.03500000000003</v>
       </c>
       <c r="F56">
-        <v>197.478</v>
+        <v>201.135</v>
       </c>
       <c r="G56">
         <v>8.51</v>
@@ -6010,28 +6010,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M56">
-        <v>10.9205334</v>
+        <v>11.1227655</v>
       </c>
       <c r="N56">
-        <v>39.30279993333333</v>
+        <v>39.10056783333333</v>
       </c>
       <c r="O56">
-        <v>7.860559986666667</v>
+        <v>7.820113566666667</v>
       </c>
       <c r="P56">
-        <v>31.44223994666667</v>
+        <v>31.28045426666666</v>
       </c>
       <c r="Q56">
-        <v>38.95223994666667</v>
+        <v>38.79045426666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1002591189146767</v>
+        <v>0.1013445024505946</v>
       </c>
       <c r="T56">
-        <v>1.033069361921974</v>
+        <v>1.053658686524306</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.598981706638371</v>
+        <v>4.515363857426763</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06993702610276756</v>
+        <v>0.07098525750478381</v>
       </c>
       <c r="C57">
-        <v>224.9570455967902</v>
+        <v>203.9199329245417</v>
       </c>
       <c r="D57">
-        <v>417.5820455967902</v>
+        <v>400.2019329245417</v>
       </c>
       <c r="E57">
-        <v>82.03500000000003</v>
+        <v>85.69200000000001</v>
       </c>
       <c r="F57">
-        <v>201.135</v>
+        <v>204.792</v>
       </c>
       <c r="G57">
         <v>8.51</v>
@@ -6092,45 +6092,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M57">
-        <v>11.1227655</v>
+        <v>11.8369776</v>
       </c>
       <c r="N57">
-        <v>39.10056783333333</v>
+        <v>38.38635573333333</v>
       </c>
       <c r="O57">
-        <v>7.820113566666667</v>
+        <v>7.677271146666667</v>
       </c>
       <c r="P57">
-        <v>31.28045426666666</v>
+        <v>30.70908458666667</v>
       </c>
       <c r="Q57">
-        <v>38.79045426666666</v>
+        <v>38.21908458666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1013445024505946</v>
+        <v>0.1024792216017814</v>
       </c>
       <c r="T57">
-        <v>1.053658686524306</v>
+        <v>1.075183889517652</v>
       </c>
       <c r="U57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.515363857426763</v>
+        <v>4.242918676582891</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07098525750478381</v>
+        <v>0.07093348890680007</v>
       </c>
       <c r="C58">
-        <v>203.9199329245417</v>
+        <v>201.0872471713504</v>
       </c>
       <c r="D58">
-        <v>400.2019329245417</v>
+        <v>401.0262471713504</v>
       </c>
       <c r="E58">
-        <v>85.69200000000001</v>
+        <v>89.34900000000002</v>
       </c>
       <c r="F58">
-        <v>204.792</v>
+        <v>208.449</v>
       </c>
       <c r="G58">
         <v>8.51</v>
@@ -6174,28 +6174,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M58">
-        <v>11.8369776</v>
+        <v>12.0483522</v>
       </c>
       <c r="N58">
-        <v>38.38635573333333</v>
+        <v>38.17498113333333</v>
       </c>
       <c r="O58">
-        <v>7.677271146666667</v>
+        <v>7.634996226666665</v>
       </c>
       <c r="P58">
-        <v>30.70908458666667</v>
+        <v>30.53998490666666</v>
       </c>
       <c r="Q58">
-        <v>38.21908458666667</v>
+        <v>38.04998490666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1024792216017814</v>
+        <v>0.1036667183879071</v>
       </c>
       <c r="T58">
-        <v>1.075183889517652</v>
+        <v>1.097710264743247</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.242918676582891</v>
+        <v>4.168481506818278</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07093348890680007</v>
+        <v>0.07088172030881632</v>
       </c>
       <c r="C59">
-        <v>201.0872471713504</v>
+        <v>198.2579641825894</v>
       </c>
       <c r="D59">
-        <v>401.0262471713504</v>
+        <v>401.8539641825894</v>
       </c>
       <c r="E59">
-        <v>89.34900000000002</v>
+        <v>93.00600000000003</v>
       </c>
       <c r="F59">
-        <v>208.449</v>
+        <v>212.106</v>
       </c>
       <c r="G59">
         <v>8.51</v>
@@ -6256,28 +6256,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M59">
-        <v>12.0483522</v>
+        <v>12.2597268</v>
       </c>
       <c r="N59">
-        <v>38.17498113333333</v>
+        <v>37.96360653333333</v>
       </c>
       <c r="O59">
-        <v>7.634996226666665</v>
+        <v>7.592721306666665</v>
       </c>
       <c r="P59">
-        <v>30.53998490666666</v>
+        <v>30.37088522666666</v>
       </c>
       <c r="Q59">
-        <v>38.04998490666666</v>
+        <v>37.88088522666666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1036667183879071</v>
+        <v>0.1049107626400388</v>
       </c>
       <c r="T59">
-        <v>1.097710264743247</v>
+        <v>1.121309324503394</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.168481506818278</v>
+        <v>4.096611136011067</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07088172030881632</v>
+        <v>0.07082995171083258</v>
       </c>
       <c r="C60">
-        <v>198.2579641825895</v>
+        <v>195.4321050717242</v>
       </c>
       <c r="D60">
-        <v>401.8539641825894</v>
+        <v>402.6851050717241</v>
       </c>
       <c r="E60">
-        <v>93.00599999999997</v>
+        <v>96.66299999999998</v>
       </c>
       <c r="F60">
-        <v>212.106</v>
+        <v>215.763</v>
       </c>
       <c r="G60">
         <v>8.51</v>
@@ -6338,28 +6338,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M60">
-        <v>12.2597268</v>
+        <v>12.4711014</v>
       </c>
       <c r="N60">
-        <v>37.96360653333333</v>
+        <v>37.75223193333333</v>
       </c>
       <c r="O60">
-        <v>7.592721306666667</v>
+        <v>7.550446386666666</v>
       </c>
       <c r="P60">
-        <v>30.37088522666667</v>
+        <v>30.20178554666666</v>
       </c>
       <c r="Q60">
-        <v>37.88088522666666</v>
+        <v>37.71178554666666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1049107626400388</v>
+        <v>0.1062154919776404</v>
       </c>
       <c r="T60">
-        <v>1.121309324503394</v>
+        <v>1.146059557910378</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.096611136011068</v>
+        <v>4.027177048960032</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07082995171083258</v>
+        <v>0.07245818311284882</v>
       </c>
       <c r="C61">
-        <v>195.4321050717242</v>
+        <v>167.1798605111159</v>
       </c>
       <c r="D61">
-        <v>402.6851050717241</v>
+        <v>378.0898605111159</v>
       </c>
       <c r="E61">
-        <v>96.66299999999998</v>
+        <v>100.32</v>
       </c>
       <c r="F61">
-        <v>215.763</v>
+        <v>219.42</v>
       </c>
       <c r="G61">
         <v>8.51</v>
@@ -6420,45 +6420,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M61">
-        <v>12.4711014</v>
+        <v>13.450446</v>
       </c>
       <c r="N61">
-        <v>37.75223193333333</v>
+        <v>36.77288733333333</v>
       </c>
       <c r="O61">
-        <v>7.550446386666666</v>
+        <v>7.354577466666666</v>
       </c>
       <c r="P61">
-        <v>30.20178554666666</v>
+        <v>29.41830986666666</v>
       </c>
       <c r="Q61">
-        <v>37.71178554666666</v>
+        <v>36.92830986666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1062154919776404</v>
+        <v>0.107585457782122</v>
       </c>
       <c r="T61">
-        <v>1.146059557910378</v>
+        <v>1.172047302987711</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.027177048960032</v>
+        <v>3.733953010430534</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07245818311284882</v>
+        <v>0.07243441451486507</v>
       </c>
       <c r="C62">
-        <v>167.1798605111159</v>
+        <v>163.8602685623125</v>
       </c>
       <c r="D62">
-        <v>378.0898605111159</v>
+        <v>378.4272685623125</v>
       </c>
       <c r="E62">
-        <v>100.32</v>
+        <v>103.977</v>
       </c>
       <c r="F62">
-        <v>219.42</v>
+        <v>223.077</v>
       </c>
       <c r="G62">
         <v>8.51</v>
@@ -6502,28 +6502,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M62">
-        <v>13.450446</v>
+        <v>13.6746201</v>
       </c>
       <c r="N62">
-        <v>36.77288733333333</v>
+        <v>36.54871323333333</v>
       </c>
       <c r="O62">
-        <v>7.354577466666666</v>
+        <v>7.309742646666667</v>
       </c>
       <c r="P62">
-        <v>29.41830986666666</v>
+        <v>29.23897058666666</v>
       </c>
       <c r="Q62">
-        <v>36.92830986666667</v>
+        <v>36.74897058666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.107585457782122</v>
+        <v>0.1090256782432438</v>
       </c>
       <c r="T62">
-        <v>1.172047302987711</v>
+        <v>1.199367752940804</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.733953010430534</v>
+        <v>3.672740665997246</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07243441451486507</v>
+        <v>0.07241064591688133</v>
       </c>
       <c r="C63">
-        <v>163.8602685623125</v>
+        <v>160.5412793584667</v>
       </c>
       <c r="D63">
-        <v>378.4272685623125</v>
+        <v>378.7652793584667</v>
       </c>
       <c r="E63">
-        <v>103.977</v>
+        <v>107.634</v>
       </c>
       <c r="F63">
-        <v>223.077</v>
+        <v>226.734</v>
       </c>
       <c r="G63">
         <v>8.51</v>
@@ -6584,28 +6584,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M63">
-        <v>13.6746201</v>
+        <v>13.8987942</v>
       </c>
       <c r="N63">
-        <v>36.54871323333333</v>
+        <v>36.32453913333333</v>
       </c>
       <c r="O63">
-        <v>7.309742646666667</v>
+        <v>7.264907826666667</v>
       </c>
       <c r="P63">
-        <v>29.23897058666666</v>
+        <v>29.05963130666667</v>
       </c>
       <c r="Q63">
-        <v>36.74897058666667</v>
+        <v>36.56963130666666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1090256782432438</v>
+        <v>0.1105416997812667</v>
       </c>
       <c r="T63">
-        <v>1.199367752940804</v>
+        <v>1.228126121312481</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.672740665997246</v>
+        <v>3.613502913319872</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07241064591688133</v>
+        <v>0.07238687731889758</v>
       </c>
       <c r="C64">
-        <v>160.5412793584667</v>
+        <v>157.2228945161361</v>
       </c>
       <c r="D64">
-        <v>378.7652793584667</v>
+        <v>379.1038945161361</v>
       </c>
       <c r="E64">
-        <v>107.634</v>
+        <v>111.291</v>
       </c>
       <c r="F64">
-        <v>226.734</v>
+        <v>230.391</v>
       </c>
       <c r="G64">
         <v>8.51</v>
@@ -6666,28 +6666,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M64">
-        <v>13.8987942</v>
+        <v>14.1229683</v>
       </c>
       <c r="N64">
-        <v>36.32453913333333</v>
+        <v>36.10036503333333</v>
       </c>
       <c r="O64">
-        <v>7.264907826666667</v>
+        <v>7.220073006666667</v>
       </c>
       <c r="P64">
-        <v>29.05963130666667</v>
+        <v>28.88029202666667</v>
       </c>
       <c r="Q64">
-        <v>36.56963130666666</v>
+        <v>36.39029202666666</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1105416997812667</v>
+        <v>0.1121396684294529</v>
       </c>
       <c r="T64">
-        <v>1.228126121312481</v>
+        <v>1.258438996082628</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.613502913319872</v>
+        <v>3.556145724219556</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07238687731889758</v>
+        <v>0.07236310872091382</v>
       </c>
       <c r="C65">
-        <v>157.2228945161361</v>
+        <v>153.9051156576637</v>
       </c>
       <c r="D65">
-        <v>379.1038945161361</v>
+        <v>379.4431156576637</v>
       </c>
       <c r="E65">
-        <v>111.291</v>
+        <v>114.948</v>
       </c>
       <c r="F65">
-        <v>230.391</v>
+        <v>234.048</v>
       </c>
       <c r="G65">
         <v>8.51</v>
@@ -6748,28 +6748,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M65">
-        <v>14.1229683</v>
+        <v>14.3471424</v>
       </c>
       <c r="N65">
-        <v>36.10036503333333</v>
+        <v>35.87619093333333</v>
       </c>
       <c r="O65">
-        <v>7.220073006666667</v>
+        <v>7.175238186666665</v>
       </c>
       <c r="P65">
-        <v>28.88029202666667</v>
+        <v>28.70095274666666</v>
       </c>
       <c r="Q65">
-        <v>36.39029202666666</v>
+        <v>36.21095274666666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1121396684294529</v>
+        <v>0.1138264131136495</v>
       </c>
       <c r="T65">
-        <v>1.258438996082628</v>
+        <v>1.290435919451116</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.556145724219556</v>
+        <v>3.500580947278625</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07236310872091382</v>
+        <v>0.07379534012293008</v>
       </c>
       <c r="C66">
-        <v>153.9051156576637</v>
+        <v>130.8359440913439</v>
       </c>
       <c r="D66">
-        <v>379.4431156576637</v>
+        <v>360.0309440913439</v>
       </c>
       <c r="E66">
-        <v>114.948</v>
+        <v>118.605</v>
       </c>
       <c r="F66">
-        <v>234.048</v>
+        <v>237.705</v>
       </c>
       <c r="G66">
         <v>8.51</v>
@@ -6830,45 +6830,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M66">
-        <v>14.3471424</v>
+        <v>15.2368905</v>
       </c>
       <c r="N66">
-        <v>35.87619093333333</v>
+        <v>34.98644283333333</v>
       </c>
       <c r="O66">
-        <v>7.175238186666665</v>
+        <v>6.997288566666666</v>
       </c>
       <c r="P66">
-        <v>28.70095274666666</v>
+        <v>27.98915426666666</v>
       </c>
       <c r="Q66">
-        <v>36.21095274666666</v>
+        <v>35.49915426666666</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1138264131136495</v>
+        <v>0.1156095432083717</v>
       </c>
       <c r="T66">
-        <v>1.290435919451116</v>
+        <v>1.32426123844066</v>
       </c>
       <c r="U66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.500580947278625</v>
+        <v>3.296166848041162</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07379534012293008</v>
+        <v>0.07379397152494635</v>
       </c>
       <c r="C67">
-        <v>130.8359440913439</v>
+        <v>127.196545653299</v>
       </c>
       <c r="D67">
-        <v>360.0309440913439</v>
+        <v>360.048545653299</v>
       </c>
       <c r="E67">
-        <v>118.605</v>
+        <v>122.262</v>
       </c>
       <c r="F67">
-        <v>237.705</v>
+        <v>241.362</v>
       </c>
       <c r="G67">
         <v>8.51</v>
@@ -6912,28 +6912,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M67">
-        <v>15.2368905</v>
+        <v>15.4713042</v>
       </c>
       <c r="N67">
-        <v>34.98644283333333</v>
+        <v>34.75202913333333</v>
       </c>
       <c r="O67">
-        <v>6.997288566666666</v>
+        <v>6.950405826666667</v>
       </c>
       <c r="P67">
-        <v>27.98915426666666</v>
+        <v>27.80162330666666</v>
       </c>
       <c r="Q67">
-        <v>35.49915426666666</v>
+        <v>35.31162330666666</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1156095432083717</v>
+        <v>0.1174975633086657</v>
       </c>
       <c r="T67">
-        <v>1.32426123844066</v>
+        <v>1.360076282076648</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.296166848041162</v>
+        <v>3.246224926101145</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07379397152494635</v>
+        <v>0.0737926029269626</v>
       </c>
       <c r="C68">
-        <v>127.196545653299</v>
+        <v>123.5571489363848</v>
       </c>
       <c r="D68">
-        <v>360.048545653299</v>
+        <v>360.0661489363848</v>
       </c>
       <c r="E68">
-        <v>122.262</v>
+        <v>125.919</v>
       </c>
       <c r="F68">
-        <v>241.362</v>
+        <v>245.019</v>
       </c>
       <c r="G68">
         <v>8.51</v>
@@ -6994,28 +6994,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M68">
-        <v>15.4713042</v>
+        <v>15.7057179</v>
       </c>
       <c r="N68">
-        <v>34.75202913333333</v>
+        <v>34.51761543333333</v>
       </c>
       <c r="O68">
-        <v>6.950405826666667</v>
+        <v>6.903523086666666</v>
       </c>
       <c r="P68">
-        <v>27.80162330666666</v>
+        <v>27.61409234666666</v>
       </c>
       <c r="Q68">
-        <v>35.31162330666666</v>
+        <v>35.12409234666666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1174975633086657</v>
+        <v>0.1195000088695836</v>
       </c>
       <c r="T68">
-        <v>1.360076282076648</v>
+        <v>1.398061934417848</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.246224926101145</v>
+        <v>3.197773807801127</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0737926029269626</v>
+        <v>0.07379123432897886</v>
       </c>
       <c r="C69">
-        <v>123.5571489363848</v>
+        <v>119.9177539408536</v>
       </c>
       <c r="D69">
-        <v>360.0661489363848</v>
+        <v>360.0837539408536</v>
       </c>
       <c r="E69">
-        <v>125.919</v>
+        <v>129.576</v>
       </c>
       <c r="F69">
-        <v>245.019</v>
+        <v>248.676</v>
       </c>
       <c r="G69">
         <v>8.51</v>
@@ -7076,28 +7076,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M69">
-        <v>15.7057179</v>
+        <v>15.9401316</v>
       </c>
       <c r="N69">
-        <v>34.51761543333333</v>
+        <v>34.28320173333333</v>
       </c>
       <c r="O69">
-        <v>6.903523086666666</v>
+        <v>6.856640346666666</v>
       </c>
       <c r="P69">
-        <v>27.61409234666666</v>
+        <v>27.42656138666666</v>
       </c>
       <c r="Q69">
-        <v>35.12409234666666</v>
+        <v>34.93656138666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1195000088695836</v>
+        <v>0.1216276072780589</v>
       </c>
       <c r="T69">
-        <v>1.398061934417848</v>
+        <v>1.438421690030372</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.197773807801127</v>
+        <v>3.150747722392287</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07379123432897886</v>
+        <v>0.07378986573099511</v>
       </c>
       <c r="C70">
-        <v>119.9177539408536</v>
+        <v>116.278360666958</v>
       </c>
       <c r="D70">
-        <v>360.0837539408536</v>
+        <v>360.101360666958</v>
       </c>
       <c r="E70">
-        <v>129.576</v>
+        <v>133.233</v>
       </c>
       <c r="F70">
-        <v>248.676</v>
+        <v>252.333</v>
       </c>
       <c r="G70">
         <v>8.51</v>
@@ -7158,28 +7158,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M70">
-        <v>15.9401316</v>
+        <v>16.1745453</v>
       </c>
       <c r="N70">
-        <v>34.28320173333333</v>
+        <v>34.04878803333332</v>
       </c>
       <c r="O70">
-        <v>6.856640346666666</v>
+        <v>6.809757606666665</v>
       </c>
       <c r="P70">
-        <v>27.42656138666666</v>
+        <v>27.23903042666666</v>
       </c>
       <c r="Q70">
-        <v>34.93656138666666</v>
+        <v>34.74903042666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1216276072780589</v>
+        <v>0.1238924700999842</v>
       </c>
       <c r="T70">
-        <v>1.438421690030372</v>
+        <v>1.481385300843705</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.150747722392287</v>
+        <v>3.105084711922833</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07378986573099511</v>
+        <v>0.07378849713301133</v>
       </c>
       <c r="C71">
-        <v>116.278360666958</v>
+        <v>112.6389691149508</v>
       </c>
       <c r="D71">
-        <v>360.101360666958</v>
+        <v>360.1189691149509</v>
       </c>
       <c r="E71">
-        <v>133.233</v>
+        <v>136.89</v>
       </c>
       <c r="F71">
-        <v>252.333</v>
+        <v>255.99</v>
       </c>
       <c r="G71">
         <v>8.51</v>
@@ -7240,28 +7240,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M71">
-        <v>16.1745453</v>
+        <v>16.408959</v>
       </c>
       <c r="N71">
-        <v>34.04878803333332</v>
+        <v>33.81437433333333</v>
       </c>
       <c r="O71">
-        <v>6.809757606666665</v>
+        <v>6.762874866666666</v>
       </c>
       <c r="P71">
-        <v>27.23903042666666</v>
+        <v>27.05149946666666</v>
       </c>
       <c r="Q71">
-        <v>34.74903042666666</v>
+        <v>34.56149946666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1238924700999842</v>
+        <v>0.1263083237767045</v>
       </c>
       <c r="T71">
-        <v>1.481385300843705</v>
+        <v>1.527213152377926</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.105084711922833</v>
+        <v>3.060726358895364</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07378849713301133</v>
+        <v>0.0737871285350276</v>
       </c>
       <c r="C72">
-        <v>112.6389691149508</v>
+        <v>108.9995792850838</v>
       </c>
       <c r="D72">
-        <v>360.1189691149509</v>
+        <v>360.1365792850838</v>
       </c>
       <c r="E72">
-        <v>136.89</v>
+        <v>140.547</v>
       </c>
       <c r="F72">
-        <v>255.99</v>
+        <v>259.647</v>
       </c>
       <c r="G72">
         <v>8.51</v>
@@ -7322,28 +7322,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M72">
-        <v>16.408959</v>
+        <v>16.6433727</v>
       </c>
       <c r="N72">
-        <v>33.81437433333333</v>
+        <v>33.57996063333333</v>
       </c>
       <c r="O72">
-        <v>6.762874866666666</v>
+        <v>6.715992126666666</v>
       </c>
       <c r="P72">
-        <v>27.05149946666666</v>
+        <v>26.86396850666666</v>
       </c>
       <c r="Q72">
-        <v>34.56149946666666</v>
+        <v>34.37396850666666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1263083237767045</v>
+        <v>0.1288907880518193</v>
       </c>
       <c r="T72">
-        <v>1.527213152377926</v>
+        <v>1.576201545397266</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.060726358895364</v>
+        <v>3.017617536939092</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07378712853502761</v>
+        <v>0.07827855993704386</v>
       </c>
       <c r="C73">
-        <v>108.9995792850836</v>
+        <v>55.53960943817106</v>
       </c>
       <c r="D73">
-        <v>360.1365792850836</v>
+        <v>310.333609438171</v>
       </c>
       <c r="E73">
-        <v>140.547</v>
+        <v>144.204</v>
       </c>
       <c r="F73">
-        <v>259.647</v>
+        <v>263.304</v>
       </c>
       <c r="G73">
         <v>8.51</v>
@@ -7404,45 +7404,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M73">
-        <v>16.6433727</v>
+        <v>18.9315576</v>
       </c>
       <c r="N73">
-        <v>33.57996063333333</v>
+        <v>31.29177573333333</v>
       </c>
       <c r="O73">
-        <v>6.715992126666666</v>
+        <v>6.258355146666666</v>
       </c>
       <c r="P73">
-        <v>26.86396850666666</v>
+        <v>25.03342058666667</v>
       </c>
       <c r="Q73">
-        <v>34.37396850666666</v>
+        <v>32.54342058666666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1288907880518193</v>
+        <v>0.1316577140608709</v>
       </c>
       <c r="T73">
-        <v>1.576201545397266</v>
+        <v>1.628689109346559</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.017617536939092</v>
+        <v>2.652889656228463</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07827855993704386</v>
+        <v>0.0783395913390601</v>
       </c>
       <c r="C74">
-        <v>55.53960943817106</v>
+        <v>51.30054634218999</v>
       </c>
       <c r="D74">
-        <v>310.333609438171</v>
+        <v>309.75154634219</v>
       </c>
       <c r="E74">
-        <v>144.204</v>
+        <v>147.861</v>
       </c>
       <c r="F74">
-        <v>263.304</v>
+        <v>266.961</v>
       </c>
       <c r="G74">
         <v>8.51</v>
@@ -7486,28 +7486,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M74">
-        <v>18.9315576</v>
+        <v>19.1944959</v>
       </c>
       <c r="N74">
-        <v>31.29177573333333</v>
+        <v>31.02883743333333</v>
       </c>
       <c r="O74">
-        <v>6.258355146666666</v>
+        <v>6.205767486666666</v>
       </c>
       <c r="P74">
-        <v>25.03342058666667</v>
+        <v>24.82306994666666</v>
       </c>
       <c r="Q74">
-        <v>32.54342058666666</v>
+        <v>32.33306994666666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1316577140608709</v>
+        <v>0.1346295975520744</v>
       </c>
       <c r="T74">
-        <v>1.628689109346559</v>
+        <v>1.685064640995799</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.652889656228463</v>
+        <v>2.616548702033551</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0783395913390601</v>
+        <v>0.07840062274107637</v>
       </c>
       <c r="C75">
-        <v>51.30054634218999</v>
+        <v>47.06366259886033</v>
       </c>
       <c r="D75">
-        <v>309.75154634219</v>
+        <v>309.1716625988603</v>
       </c>
       <c r="E75">
-        <v>147.861</v>
+        <v>151.518</v>
       </c>
       <c r="F75">
-        <v>266.961</v>
+        <v>270.618</v>
       </c>
       <c r="G75">
         <v>8.51</v>
@@ -7568,28 +7568,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M75">
-        <v>19.1944959</v>
+        <v>19.4574342</v>
       </c>
       <c r="N75">
-        <v>31.02883743333333</v>
+        <v>30.76589913333333</v>
       </c>
       <c r="O75">
-        <v>6.205767486666666</v>
+        <v>6.153179826666666</v>
       </c>
       <c r="P75">
-        <v>24.82306994666666</v>
+        <v>24.61271930666666</v>
       </c>
       <c r="Q75">
-        <v>32.33306994666666</v>
+        <v>32.12271930666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1346295975520744</v>
+        <v>0.1378300874656783</v>
       </c>
       <c r="T75">
-        <v>1.685064640995799</v>
+        <v>1.745776752002674</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.616548702033551</v>
+        <v>2.581189935789855</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07840062274107637</v>
+        <v>0.07846165414309261</v>
       </c>
       <c r="C76">
-        <v>47.06366259886033</v>
+        <v>42.82894599120067</v>
       </c>
       <c r="D76">
-        <v>309.1716625988603</v>
+        <v>308.5939459912007</v>
       </c>
       <c r="E76">
-        <v>151.518</v>
+        <v>155.175</v>
       </c>
       <c r="F76">
-        <v>270.618</v>
+        <v>274.275</v>
       </c>
       <c r="G76">
         <v>8.51</v>
@@ -7650,28 +7650,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M76">
-        <v>19.4574342</v>
+        <v>19.7203725</v>
       </c>
       <c r="N76">
-        <v>30.76589913333333</v>
+        <v>30.50296083333333</v>
       </c>
       <c r="O76">
-        <v>6.153179826666666</v>
+        <v>6.100592166666666</v>
       </c>
       <c r="P76">
-        <v>24.61271930666666</v>
+        <v>24.40236866666666</v>
       </c>
       <c r="Q76">
-        <v>32.12271930666666</v>
+        <v>31.91236866666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1378300874656783</v>
+        <v>0.1412866165723704</v>
       </c>
       <c r="T76">
-        <v>1.745776752002674</v>
+        <v>1.811345831890098</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.581189935789855</v>
+        <v>2.546774069979324</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07846165414309261</v>
+        <v>0.07852268554510887</v>
       </c>
       <c r="C77">
-        <v>42.82894599120067</v>
+        <v>38.59638439337249</v>
       </c>
       <c r="D77">
-        <v>308.5939459912007</v>
+        <v>308.0183843933725</v>
       </c>
       <c r="E77">
-        <v>155.175</v>
+        <v>158.832</v>
       </c>
       <c r="F77">
-        <v>274.275</v>
+        <v>277.932</v>
       </c>
       <c r="G77">
         <v>8.51</v>
@@ -7732,28 +7732,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M77">
-        <v>19.7203725</v>
+        <v>19.9833108</v>
       </c>
       <c r="N77">
-        <v>30.50296083333333</v>
+        <v>30.24002253333333</v>
       </c>
       <c r="O77">
-        <v>6.100592166666666</v>
+        <v>6.048004506666666</v>
       </c>
       <c r="P77">
-        <v>24.40236866666666</v>
+        <v>24.19201802666666</v>
       </c>
       <c r="Q77">
-        <v>31.91236866666667</v>
+        <v>31.70201802666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1412866165723704</v>
+        <v>0.1450311897712869</v>
       </c>
       <c r="T77">
-        <v>1.811345831890098</v>
+        <v>1.882379001768141</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.546774069979324</v>
+        <v>2.513263884848016</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07852268554510887</v>
+        <v>0.08098611694712513</v>
       </c>
       <c r="C78">
-        <v>38.59638439337249</v>
+        <v>13.37456774556836</v>
       </c>
       <c r="D78">
-        <v>308.0183843933725</v>
+        <v>286.4535677455684</v>
       </c>
       <c r="E78">
-        <v>158.832</v>
+        <v>162.489</v>
       </c>
       <c r="F78">
-        <v>277.932</v>
+        <v>281.589</v>
       </c>
       <c r="G78">
         <v>8.51</v>
@@ -7814,45 +7814,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M78">
-        <v>19.9833108</v>
+        <v>21.3444462</v>
       </c>
       <c r="N78">
-        <v>30.24002253333333</v>
+        <v>28.87888713333333</v>
       </c>
       <c r="O78">
-        <v>6.048004506666666</v>
+        <v>5.775777426666666</v>
       </c>
       <c r="P78">
-        <v>24.19201802666666</v>
+        <v>23.10310970666666</v>
       </c>
       <c r="Q78">
-        <v>31.70201802666666</v>
+        <v>30.61310970666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1450311897712869</v>
+        <v>0.1491013780309788</v>
       </c>
       <c r="T78">
-        <v>1.882379001768141</v>
+        <v>1.959588969026884</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.513263884848016</v>
+        <v>2.352993039160385</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08098611694712513</v>
+        <v>0.08107834834914138</v>
       </c>
       <c r="C79">
-        <v>13.37456774556836</v>
+        <v>8.968666070686709</v>
       </c>
       <c r="D79">
-        <v>286.4535677455684</v>
+        <v>285.7046660706867</v>
       </c>
       <c r="E79">
-        <v>162.489</v>
+        <v>166.146</v>
       </c>
       <c r="F79">
-        <v>281.589</v>
+        <v>285.246</v>
       </c>
       <c r="G79">
         <v>8.51</v>
@@ -7896,28 +7896,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M79">
-        <v>21.3444462</v>
+        <v>21.6216468</v>
       </c>
       <c r="N79">
-        <v>28.87888713333333</v>
+        <v>28.60168653333333</v>
       </c>
       <c r="O79">
-        <v>5.775777426666666</v>
+        <v>5.720337306666666</v>
       </c>
       <c r="P79">
-        <v>23.10310970666666</v>
+        <v>22.88134922666666</v>
       </c>
       <c r="Q79">
-        <v>30.61310970666666</v>
+        <v>30.39134922666666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1491013780309788</v>
+        <v>0.1535415834051881</v>
       </c>
       <c r="T79">
-        <v>1.959588969026884</v>
+        <v>2.043818024218239</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.352993039160385</v>
+        <v>2.322826461735252</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08107834834914138</v>
+        <v>0.08117057975115763</v>
       </c>
       <c r="C80">
-        <v>8.968666070686709</v>
+        <v>4.566670028787655</v>
       </c>
       <c r="D80">
-        <v>285.7046660706867</v>
+        <v>284.9596700287877</v>
       </c>
       <c r="E80">
-        <v>166.146</v>
+        <v>169.803</v>
       </c>
       <c r="F80">
-        <v>285.246</v>
+        <v>288.903</v>
       </c>
       <c r="G80">
         <v>8.51</v>
@@ -7978,28 +7978,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M80">
-        <v>21.6216468</v>
+        <v>21.8988474</v>
       </c>
       <c r="N80">
-        <v>28.60168653333333</v>
+        <v>28.32448593333332</v>
       </c>
       <c r="O80">
-        <v>5.720337306666666</v>
+        <v>5.664897186666665</v>
       </c>
       <c r="P80">
-        <v>22.88134922666666</v>
+        <v>22.65958874666666</v>
       </c>
       <c r="Q80">
-        <v>30.39134922666666</v>
+        <v>30.16958874666666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1535415834051881</v>
+        <v>0.158404665481703</v>
       </c>
       <c r="T80">
-        <v>2.043818024218239</v>
+        <v>2.136068894189724</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.322826461735252</v>
+        <v>2.293423595131007</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08117057975115763</v>
+        <v>0.08126281115317388</v>
       </c>
       <c r="C81">
-        <v>4.566670028787655</v>
+        <v>0.1685491466522535</v>
       </c>
       <c r="D81">
-        <v>284.9596700287877</v>
+        <v>284.2185491466523</v>
       </c>
       <c r="E81">
-        <v>169.803</v>
+        <v>173.46</v>
       </c>
       <c r="F81">
-        <v>288.903</v>
+        <v>292.56</v>
       </c>
       <c r="G81">
         <v>8.51</v>
@@ -8060,28 +8060,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M81">
-        <v>21.8988474</v>
+        <v>22.176048</v>
       </c>
       <c r="N81">
-        <v>28.32448593333332</v>
+        <v>28.04728533333333</v>
       </c>
       <c r="O81">
-        <v>5.664897186666665</v>
+        <v>5.609457066666666</v>
       </c>
       <c r="P81">
-        <v>22.65958874666666</v>
+        <v>22.43782826666666</v>
       </c>
       <c r="Q81">
-        <v>30.16958874666666</v>
+        <v>29.94782826666666</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.158404665481703</v>
+        <v>0.1637540557658694</v>
       </c>
       <c r="T81">
-        <v>2.136068894189724</v>
+        <v>2.237544851158357</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.293423595131007</v>
+        <v>2.26475580019187</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08126281115317388</v>
+        <v>0.08135504255519013</v>
       </c>
       <c r="C82">
-        <v>0.1685491466522535</v>
+        <v>-4.225726732743226</v>
       </c>
       <c r="D82">
-        <v>284.2185491466523</v>
+        <v>283.4812732672568</v>
       </c>
       <c r="E82">
-        <v>173.46</v>
+        <v>177.117</v>
       </c>
       <c r="F82">
-        <v>292.56</v>
+        <v>296.217</v>
       </c>
       <c r="G82">
         <v>8.51</v>
@@ -8142,28 +8142,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M82">
-        <v>22.176048</v>
+        <v>22.4532486</v>
       </c>
       <c r="N82">
-        <v>28.04728533333333</v>
+        <v>27.77008473333333</v>
       </c>
       <c r="O82">
-        <v>5.609457066666666</v>
+        <v>5.554016946666666</v>
       </c>
       <c r="P82">
-        <v>22.43782826666666</v>
+        <v>22.21606778666666</v>
       </c>
       <c r="Q82">
-        <v>29.94782826666666</v>
+        <v>29.72606778666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1637540557658694</v>
+        <v>0.1696665397641586</v>
       </c>
       <c r="T82">
-        <v>2.237544851158357</v>
+        <v>2.349702487807899</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.26475580019187</v>
+        <v>2.236795852041353</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08135504255519013</v>
+        <v>0.08144727395720638</v>
       </c>
       <c r="C83">
-        <v>-4.225726732743226</v>
+        <v>-8.616187454317014</v>
       </c>
       <c r="D83">
-        <v>283.4812732672568</v>
+        <v>282.747812545683</v>
       </c>
       <c r="E83">
-        <v>177.117</v>
+        <v>180.774</v>
       </c>
       <c r="F83">
-        <v>296.217</v>
+        <v>299.874</v>
       </c>
       <c r="G83">
         <v>8.51</v>
@@ -8224,28 +8224,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M83">
-        <v>22.4532486</v>
+        <v>22.7304492</v>
       </c>
       <c r="N83">
-        <v>27.77008473333333</v>
+        <v>27.49288413333333</v>
       </c>
       <c r="O83">
-        <v>5.554016946666666</v>
+        <v>5.498576826666666</v>
       </c>
       <c r="P83">
-        <v>22.21606778666666</v>
+        <v>21.99430730666666</v>
       </c>
       <c r="Q83">
-        <v>29.72606778666666</v>
+        <v>29.50430730666666</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1696665397641586</v>
+        <v>0.1762359664289244</v>
       </c>
       <c r="T83">
-        <v>2.349702487807899</v>
+        <v>2.474322084085167</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.236795852041353</v>
+        <v>2.209517853845727</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08144727395720638</v>
+        <v>0.08153950535922264</v>
       </c>
       <c r="C84">
-        <v>-8.616187454317014</v>
+        <v>-13.00286255490948</v>
       </c>
       <c r="D84">
-        <v>282.747812545683</v>
+        <v>282.0181374450905</v>
       </c>
       <c r="E84">
-        <v>180.774</v>
+        <v>184.431</v>
       </c>
       <c r="F84">
-        <v>299.874</v>
+        <v>303.531</v>
       </c>
       <c r="G84">
         <v>8.51</v>
@@ -8306,28 +8306,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M84">
-        <v>22.7304492</v>
+        <v>23.0076498</v>
       </c>
       <c r="N84">
-        <v>27.49288413333333</v>
+        <v>27.21568353333333</v>
       </c>
       <c r="O84">
-        <v>5.498576826666666</v>
+        <v>5.443136706666666</v>
       </c>
       <c r="P84">
-        <v>21.99430730666666</v>
+        <v>21.77254682666666</v>
       </c>
       <c r="Q84">
-        <v>29.50430730666666</v>
+        <v>29.28254682666666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1762359664289244</v>
+        <v>0.1835782668189567</v>
       </c>
       <c r="T84">
-        <v>2.474322084085167</v>
+        <v>2.613602809336232</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.209517853845727</v>
+        <v>2.182897156811441</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08153950535922264</v>
+        <v>0.08163173676123889</v>
       </c>
       <c r="C85">
-        <v>-13.00286255490948</v>
+        <v>-17.38578126724809</v>
       </c>
       <c r="D85">
-        <v>282.0181374450905</v>
+        <v>281.292218732752</v>
       </c>
       <c r="E85">
-        <v>184.431</v>
+        <v>188.0880000000001</v>
       </c>
       <c r="F85">
-        <v>303.531</v>
+        <v>307.188</v>
       </c>
       <c r="G85">
         <v>8.51</v>
@@ -8388,28 +8388,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M85">
-        <v>23.0076498</v>
+        <v>23.28485040000001</v>
       </c>
       <c r="N85">
-        <v>27.21568353333333</v>
+        <v>26.93848293333332</v>
       </c>
       <c r="O85">
-        <v>5.443136706666666</v>
+        <v>5.387696586666665</v>
       </c>
       <c r="P85">
-        <v>21.77254682666666</v>
+        <v>21.55078634666666</v>
       </c>
       <c r="Q85">
-        <v>29.28254682666666</v>
+        <v>29.06078634666666</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1835782668189567</v>
+        <v>0.1918383547577431</v>
       </c>
       <c r="T85">
-        <v>2.613602809336232</v>
+        <v>2.770293625243681</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.182897156811441</v>
+        <v>2.156910285897019</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08163173676123889</v>
+        <v>0.08172396816325514</v>
       </c>
       <c r="C86">
-        <v>-17.38578126724803</v>
+        <v>-21.76497252385093</v>
       </c>
       <c r="D86">
-        <v>281.292218732752</v>
+        <v>280.5700274761491</v>
       </c>
       <c r="E86">
-        <v>188.088</v>
+        <v>191.745</v>
       </c>
       <c r="F86">
-        <v>307.188</v>
+        <v>310.845</v>
       </c>
       <c r="G86">
         <v>8.51</v>
@@ -8470,28 +8470,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M86">
-        <v>23.2848504</v>
+        <v>23.562051</v>
       </c>
       <c r="N86">
-        <v>26.93848293333333</v>
+        <v>26.66128233333333</v>
       </c>
       <c r="O86">
-        <v>5.387696586666666</v>
+        <v>5.332256466666666</v>
       </c>
       <c r="P86">
-        <v>21.55078634666666</v>
+        <v>21.32902586666666</v>
       </c>
       <c r="Q86">
-        <v>29.06078634666666</v>
+        <v>28.83902586666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.191838354757743</v>
+        <v>0.2011997877550342</v>
       </c>
       <c r="T86">
-        <v>2.770293625243679</v>
+        <v>2.947876549938787</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.15691028589702</v>
+        <v>2.131534870768819</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08172396816325514</v>
+        <v>0.08181619956527139</v>
       </c>
       <c r="C87">
-        <v>-21.76497252385093</v>
+        <v>-26.14046496087133</v>
       </c>
       <c r="D87">
-        <v>280.5700274761491</v>
+        <v>279.8515350391287</v>
       </c>
       <c r="E87">
-        <v>191.745</v>
+        <v>195.402</v>
       </c>
       <c r="F87">
-        <v>310.845</v>
+        <v>314.502</v>
       </c>
       <c r="G87">
         <v>8.51</v>
@@ -8552,28 +8552,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M87">
-        <v>23.562051</v>
+        <v>23.8392516</v>
       </c>
       <c r="N87">
-        <v>26.66128233333333</v>
+        <v>26.38408173333332</v>
       </c>
       <c r="O87">
-        <v>5.332256466666666</v>
+        <v>5.276816346666665</v>
       </c>
       <c r="P87">
-        <v>21.32902586666666</v>
+        <v>21.10726538666666</v>
       </c>
       <c r="Q87">
-        <v>28.83902586666666</v>
+        <v>28.61726538666666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2011997877550342</v>
+        <v>0.2118985683233671</v>
       </c>
       <c r="T87">
-        <v>2.947876549938787</v>
+        <v>3.150828463876053</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.131534870768819</v>
+        <v>2.106749581573832</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08181619956527139</v>
+        <v>0.08190843096728764</v>
       </c>
       <c r="C88">
-        <v>-26.14046496087133</v>
+        <v>-30.51228692188209</v>
       </c>
       <c r="D88">
-        <v>279.8515350391287</v>
+        <v>279.1367130781179</v>
       </c>
       <c r="E88">
-        <v>195.402</v>
+        <v>199.059</v>
       </c>
       <c r="F88">
-        <v>314.502</v>
+        <v>318.159</v>
       </c>
       <c r="G88">
         <v>8.51</v>
@@ -8634,28 +8634,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M88">
-        <v>23.8392516</v>
+        <v>24.1164522</v>
       </c>
       <c r="N88">
-        <v>26.38408173333332</v>
+        <v>26.10688113333333</v>
       </c>
       <c r="O88">
-        <v>5.276816346666665</v>
+        <v>5.221376226666666</v>
       </c>
       <c r="P88">
-        <v>21.10726538666666</v>
+        <v>20.88550490666666</v>
       </c>
       <c r="Q88">
-        <v>28.61726538666666</v>
+        <v>28.39550490666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2118985683233671</v>
+        <v>0.2242433151329818</v>
       </c>
       <c r="T88">
-        <v>3.150828463876053</v>
+        <v>3.385003749188283</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.106749581573832</v>
+        <v>2.08253406914195</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08190843096728764</v>
+        <v>0.08200066236930389</v>
       </c>
       <c r="C89">
-        <v>-30.51228692188209</v>
+        <v>-34.88046646160325</v>
       </c>
       <c r="D89">
-        <v>279.1367130781179</v>
+        <v>278.4255335383967</v>
       </c>
       <c r="E89">
-        <v>199.059</v>
+        <v>202.716</v>
       </c>
       <c r="F89">
-        <v>318.159</v>
+        <v>321.816</v>
       </c>
       <c r="G89">
         <v>8.51</v>
@@ -8716,28 +8716,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M89">
-        <v>24.1164522</v>
+        <v>24.3936528</v>
       </c>
       <c r="N89">
-        <v>26.10688113333333</v>
+        <v>25.82968053333333</v>
       </c>
       <c r="O89">
-        <v>5.221376226666666</v>
+        <v>5.165936106666666</v>
       </c>
       <c r="P89">
-        <v>20.88550490666666</v>
+        <v>20.66374442666666</v>
       </c>
       <c r="Q89">
-        <v>28.39550490666666</v>
+        <v>28.17374442666666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2242433151329818</v>
+        <v>0.2386455197441991</v>
       </c>
       <c r="T89">
-        <v>3.385003749188283</v>
+        <v>3.658208248719218</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.08253406914195</v>
+        <v>2.058868909265337</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08200066236930389</v>
+        <v>0.08209289377132015</v>
       </c>
       <c r="C90">
-        <v>-34.88046646160325</v>
+        <v>-39.24503134957212</v>
       </c>
       <c r="D90">
-        <v>278.4255335383967</v>
+        <v>277.7179686504279</v>
       </c>
       <c r="E90">
-        <v>202.716</v>
+        <v>206.373</v>
       </c>
       <c r="F90">
-        <v>321.816</v>
+        <v>325.473</v>
       </c>
       <c r="G90">
         <v>8.51</v>
@@ -8798,28 +8798,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M90">
-        <v>24.3936528</v>
+        <v>24.6708534</v>
       </c>
       <c r="N90">
-        <v>25.82968053333333</v>
+        <v>25.55247993333333</v>
       </c>
       <c r="O90">
-        <v>5.165936106666666</v>
+        <v>5.110495986666666</v>
       </c>
       <c r="P90">
-        <v>20.66374442666666</v>
+        <v>20.44198394666666</v>
       </c>
       <c r="Q90">
-        <v>28.17374442666666</v>
+        <v>27.95198394666666</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2386455197441991</v>
+        <v>0.2556663070120013</v>
       </c>
       <c r="T90">
-        <v>3.658208248719218</v>
+        <v>3.981086293619414</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.058868909265337</v>
+        <v>2.035735550734265</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08209289377132015</v>
+        <v>0.08218512517333641</v>
       </c>
       <c r="C91">
-        <v>-39.24503134957212</v>
+        <v>-43.60600907375789</v>
       </c>
       <c r="D91">
-        <v>277.7179686504279</v>
+        <v>277.0139909262421</v>
       </c>
       <c r="E91">
-        <v>206.373</v>
+        <v>210.03</v>
       </c>
       <c r="F91">
-        <v>325.473</v>
+        <v>329.13</v>
       </c>
       <c r="G91">
         <v>8.51</v>
@@ -8880,28 +8880,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M91">
-        <v>24.6708534</v>
+        <v>24.948054</v>
       </c>
       <c r="N91">
-        <v>25.55247993333333</v>
+        <v>25.27527933333333</v>
       </c>
       <c r="O91">
-        <v>5.110495986666666</v>
+        <v>5.055055866666666</v>
       </c>
       <c r="P91">
-        <v>20.44198394666666</v>
+        <v>20.22022346666666</v>
       </c>
       <c r="Q91">
-        <v>27.95198394666666</v>
+        <v>27.73022346666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2556663070120013</v>
+        <v>0.2760912517333641</v>
       </c>
       <c r="T91">
-        <v>3.981086293619414</v>
+        <v>4.36853994749965</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.035735550734265</v>
+        <v>2.013116266837218</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08218512517333641</v>
+        <v>0.09261495657535265</v>
       </c>
       <c r="C92">
-        <v>-43.60600907375789</v>
+        <v>-108.9785254965903</v>
       </c>
       <c r="D92">
-        <v>277.0139909262421</v>
+        <v>215.2984745034097</v>
       </c>
       <c r="E92">
-        <v>210.03</v>
+        <v>213.687</v>
       </c>
       <c r="F92">
-        <v>329.13</v>
+        <v>332.787</v>
       </c>
       <c r="G92">
         <v>8.51</v>
@@ -8962,45 +8962,45 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M92">
-        <v>24.948054</v>
+        <v>29.95083</v>
       </c>
       <c r="N92">
-        <v>25.27527933333333</v>
+        <v>20.27250333333333</v>
       </c>
       <c r="O92">
-        <v>5.055055866666666</v>
+        <v>4.054500666666667</v>
       </c>
       <c r="P92">
-        <v>20.22022346666666</v>
+        <v>16.21800266666667</v>
       </c>
       <c r="Q92">
-        <v>27.73022346666666</v>
+        <v>23.72800266666667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2760912517333641</v>
+        <v>0.301055073059474</v>
       </c>
       <c r="T92">
-        <v>4.36853994749965</v>
+        <v>4.84209441335327</v>
       </c>
       <c r="U92">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V92">
         <v>0.2</v>
       </c>
       <c r="W92">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.013116266837218</v>
+        <v>1.676859483805068</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09261495657535265</v>
+        <v>0.0928207879773689</v>
       </c>
       <c r="C93">
-        <v>-108.9785254965903</v>
+        <v>-113.5779849653751</v>
       </c>
       <c r="D93">
-        <v>215.2984745034097</v>
+        <v>214.356015034625</v>
       </c>
       <c r="E93">
-        <v>213.687</v>
+        <v>217.344</v>
       </c>
       <c r="F93">
-        <v>332.787</v>
+        <v>336.444</v>
       </c>
       <c r="G93">
         <v>8.51</v>
@@ -9044,28 +9044,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M93">
-        <v>29.95083</v>
+        <v>30.27996</v>
       </c>
       <c r="N93">
-        <v>20.27250333333333</v>
+        <v>19.94337333333333</v>
       </c>
       <c r="O93">
-        <v>4.054500666666667</v>
+        <v>3.988674666666666</v>
       </c>
       <c r="P93">
-        <v>16.21800266666667</v>
+        <v>15.95469866666666</v>
       </c>
       <c r="Q93">
-        <v>23.72800266666667</v>
+        <v>23.46469866666666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.301055073059474</v>
+        <v>0.3322598497171115</v>
       </c>
       <c r="T93">
-        <v>4.84209441335327</v>
+        <v>5.434037495670298</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.676859483805068</v>
+        <v>1.658632750285447</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0928207879773689</v>
+        <v>0.09302661937938514</v>
       </c>
       <c r="C94">
-        <v>-113.5779849653751</v>
+        <v>-118.1692292472017</v>
       </c>
       <c r="D94">
-        <v>214.356015034625</v>
+        <v>213.4217707527983</v>
       </c>
       <c r="E94">
-        <v>217.344</v>
+        <v>221.001</v>
       </c>
       <c r="F94">
-        <v>336.444</v>
+        <v>340.101</v>
       </c>
       <c r="G94">
         <v>8.51</v>
@@ -9126,28 +9126,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M94">
-        <v>30.27996</v>
+        <v>30.60909</v>
       </c>
       <c r="N94">
-        <v>19.94337333333333</v>
+        <v>19.61424333333333</v>
       </c>
       <c r="O94">
-        <v>3.988674666666666</v>
+        <v>3.922848666666666</v>
       </c>
       <c r="P94">
-        <v>15.95469866666666</v>
+        <v>15.69139466666666</v>
       </c>
       <c r="Q94">
-        <v>23.46469866666666</v>
+        <v>23.20139466666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3322598497171115</v>
+        <v>0.3723802768483596</v>
       </c>
       <c r="T94">
-        <v>5.434037495670298</v>
+        <v>6.195107172935046</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.658632750285447</v>
+        <v>1.64079798952969</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09302661937938514</v>
+        <v>0.09323245078140141</v>
       </c>
       <c r="C95">
-        <v>-118.1692292472017</v>
+        <v>-122.7523652905889</v>
       </c>
       <c r="D95">
-        <v>213.4217707527983</v>
+        <v>212.4956347094111</v>
       </c>
       <c r="E95">
-        <v>221.001</v>
+        <v>224.658</v>
       </c>
       <c r="F95">
-        <v>340.101</v>
+        <v>343.758</v>
       </c>
       <c r="G95">
         <v>8.51</v>
@@ -9208,28 +9208,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M95">
-        <v>30.60909</v>
+        <v>30.93822</v>
       </c>
       <c r="N95">
-        <v>19.61424333333333</v>
+        <v>19.28511333333333</v>
       </c>
       <c r="O95">
-        <v>3.922848666666666</v>
+        <v>3.857022666666666</v>
       </c>
       <c r="P95">
-        <v>15.69139466666666</v>
+        <v>15.42809066666666</v>
       </c>
       <c r="Q95">
-        <v>23.20139466666667</v>
+        <v>22.93809066666666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3723802768483596</v>
+        <v>0.4258741796900238</v>
       </c>
       <c r="T95">
-        <v>6.195107172935046</v>
+        <v>7.209866742621378</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.64079798952969</v>
+        <v>1.623342691768735</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09323245078140141</v>
+        <v>0.09343828218341765</v>
       </c>
       <c r="C96">
-        <v>-122.7523652905889</v>
+        <v>-127.3274981956791</v>
       </c>
       <c r="D96">
-        <v>212.4956347094111</v>
+        <v>211.5775018043209</v>
       </c>
       <c r="E96">
-        <v>224.658</v>
+        <v>228.315</v>
       </c>
       <c r="F96">
-        <v>343.758</v>
+        <v>347.415</v>
       </c>
       <c r="G96">
         <v>8.51</v>
@@ -9290,28 +9290,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M96">
-        <v>30.93822</v>
+        <v>31.26735</v>
       </c>
       <c r="N96">
-        <v>19.28511333333333</v>
+        <v>18.95598333333333</v>
       </c>
       <c r="O96">
-        <v>3.857022666666666</v>
+        <v>3.791196666666666</v>
       </c>
       <c r="P96">
-        <v>15.42809066666666</v>
+        <v>15.16478666666666</v>
       </c>
       <c r="Q96">
-        <v>22.93809066666666</v>
+        <v>22.67478666666666</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4258741796900238</v>
+        <v>0.5007656436683539</v>
       </c>
       <c r="T96">
-        <v>7.209866742621378</v>
+        <v>8.630530140182245</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.623342691768735</v>
+        <v>1.606254873960644</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09343828218341765</v>
+        <v>0.09364411358543391</v>
       </c>
       <c r="C97">
-        <v>-127.3274981956791</v>
+        <v>-131.8947312539991</v>
       </c>
       <c r="D97">
-        <v>211.5775018043209</v>
+        <v>210.6672687460009</v>
       </c>
       <c r="E97">
-        <v>228.315</v>
+        <v>231.972</v>
       </c>
       <c r="F97">
-        <v>347.415</v>
+        <v>351.072</v>
       </c>
       <c r="G97">
         <v>8.51</v>
@@ -9372,28 +9372,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M97">
-        <v>31.26735</v>
+        <v>31.59648</v>
       </c>
       <c r="N97">
-        <v>18.95598333333333</v>
+        <v>18.62685333333333</v>
       </c>
       <c r="O97">
-        <v>3.791196666666666</v>
+        <v>3.725370666666666</v>
       </c>
       <c r="P97">
-        <v>15.16478666666666</v>
+        <v>14.90148266666666</v>
       </c>
       <c r="Q97">
-        <v>22.67478666666666</v>
+        <v>22.41148266666666</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5007656436683539</v>
+        <v>0.6131028396358489</v>
       </c>
       <c r="T97">
-        <v>8.630530140182245</v>
+        <v>10.76152523652354</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.606254873960644</v>
+        <v>1.589523052356887</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09364411358543391</v>
+        <v>0.09384994498745017</v>
       </c>
       <c r="C98">
-        <v>-131.8947312539991</v>
+        <v>-136.454165987197</v>
       </c>
       <c r="D98">
-        <v>210.6672687460009</v>
+        <v>209.764834012803</v>
       </c>
       <c r="E98">
-        <v>231.972</v>
+        <v>235.629</v>
       </c>
       <c r="F98">
-        <v>351.072</v>
+        <v>354.729</v>
       </c>
       <c r="G98">
         <v>8.51</v>
@@ -9454,28 +9454,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M98">
-        <v>31.59648</v>
+        <v>31.92561</v>
       </c>
       <c r="N98">
-        <v>18.62685333333333</v>
+        <v>18.29772333333333</v>
       </c>
       <c r="O98">
-        <v>3.725370666666666</v>
+        <v>3.659544666666666</v>
       </c>
       <c r="P98">
-        <v>14.90148266666666</v>
+        <v>14.63817866666666</v>
       </c>
       <c r="Q98">
-        <v>22.41148266666666</v>
+        <v>22.14817866666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6131028396358474</v>
+        <v>0.8003314995816716</v>
       </c>
       <c r="T98">
-        <v>10.76152523652352</v>
+        <v>14.31318373042567</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.589523052356887</v>
+        <v>1.573136216765579</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09384994498745017</v>
+        <v>0.09405577638946641</v>
       </c>
       <c r="C99">
-        <v>-136.454165987197</v>
+        <v>-141.005902184789</v>
       </c>
       <c r="D99">
-        <v>209.764834012803</v>
+        <v>208.870097815211</v>
       </c>
       <c r="E99">
-        <v>235.629</v>
+        <v>239.286</v>
       </c>
       <c r="F99">
-        <v>354.729</v>
+        <v>358.386</v>
       </c>
       <c r="G99">
         <v>8.51</v>
@@ -9536,28 +9536,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M99">
-        <v>31.92561</v>
+        <v>32.25474</v>
       </c>
       <c r="N99">
-        <v>18.29772333333333</v>
+        <v>17.96859333333333</v>
       </c>
       <c r="O99">
-        <v>3.659544666666666</v>
+        <v>3.593718666666666</v>
       </c>
       <c r="P99">
-        <v>14.63817866666666</v>
+        <v>14.37487466666667</v>
       </c>
       <c r="Q99">
-        <v>22.14817866666667</v>
+        <v>21.88487466666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8003314995816716</v>
+        <v>1.17478881947332</v>
       </c>
       <c r="T99">
-        <v>14.31318373042567</v>
+        <v>21.41650071822997</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.573136216765579</v>
+        <v>1.55708380639042</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09405577638946641</v>
+        <v>0.09426160779148267</v>
       </c>
       <c r="C100">
-        <v>-141.005902184789</v>
+        <v>-145.5500379409439</v>
       </c>
       <c r="D100">
-        <v>208.870097815211</v>
+        <v>207.9829620590561</v>
       </c>
       <c r="E100">
-        <v>239.286</v>
+        <v>242.943</v>
       </c>
       <c r="F100">
-        <v>358.386</v>
+        <v>362.043</v>
       </c>
       <c r="G100">
         <v>8.51</v>
@@ -9618,28 +9618,28 @@
         <v>50.22333333333333</v>
       </c>
       <c r="M100">
-        <v>32.25474</v>
+        <v>32.58387</v>
       </c>
       <c r="N100">
-        <v>17.96859333333333</v>
+        <v>17.63946333333333</v>
       </c>
       <c r="O100">
-        <v>3.593718666666666</v>
+        <v>3.527892666666666</v>
       </c>
       <c r="P100">
-        <v>14.37487466666667</v>
+        <v>14.11157066666667</v>
       </c>
       <c r="Q100">
-        <v>21.88487466666666</v>
+        <v>21.62157066666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.17478881947332</v>
+        <v>2.298160779148265</v>
       </c>
       <c r="T100">
-        <v>21.41650071822997</v>
+        <v>42.72645168164286</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.55708380639042</v>
+        <v>1.541355687133951</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09426160779148267</v>
-      </c>
-      <c r="C101">
-        <v>-145.5500379409439</v>
-      </c>
-      <c r="D101">
-        <v>207.9829620590561</v>
-      </c>
-      <c r="E101">
-        <v>242.943</v>
-      </c>
-      <c r="F101">
-        <v>362.043</v>
-      </c>
-      <c r="G101">
-        <v>8.51</v>
-      </c>
-      <c r="H101">
-        <v>246.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>57.73333333333333</v>
-      </c>
-      <c r="K101">
-        <v>7.51</v>
-      </c>
-      <c r="L101">
-        <v>50.22333333333333</v>
-      </c>
-      <c r="M101">
-        <v>32.58387</v>
-      </c>
-      <c r="N101">
-        <v>17.63946333333333</v>
-      </c>
-      <c r="O101">
-        <v>3.527892666666666</v>
-      </c>
-      <c r="P101">
-        <v>14.11157066666667</v>
-      </c>
-      <c r="Q101">
-        <v>21.62157066666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.298160779148265</v>
-      </c>
-      <c r="T101">
-        <v>42.72645168164286</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.541355687133951</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
